--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J56"/>
+  <dimension ref="A1:J57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2545,6 +2545,44 @@
       </c>
       <c r="F56" t="n">
         <v>101.2127685546875</v>
+      </c>
+      <c r="G56" t="n">
+        <v>101.6800003051758</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.4672317504882812</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.4595119483536213</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.4247653238735712</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-09-13 04:31:04</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>24</v>
+      </c>
+      <c r="F57" t="n">
+        <v>101.7695770263672</v>
       </c>
     </row>
   </sheetData>
@@ -2558,7 +2596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M56"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5949,6 +5987,24 @@
           <t>101.491920,101.446304,101.501923,101.538452,101.470413,101.483307,101.483963,101.422272,101.391502,101.368286,101.375961,101.366974,101.365868,101.321869,101.419624,101.330215,101.339142,101.354439,101.316368,101.335724,101.341309,101.291931,101.159210,101.212769</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>101.639999,101.680000,101.650002,101.820000,101.980003,102.120003,102.110001,102.029999,101.949997,101.980003,102.040001,102.059998,101.930000,101.629997,101.260002,101.339996,101.470001,101.650002,101.739998,101.709999,102.250000,101.879997,101.599998,101.680000</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>0.148079,0.233696,0.148079,0.281548,0.509590,0.636696,0.626038,0.607727,0.558495,0.611717,0.664040,0.693024,0.564132,0.308128,0.159622,0.009781,0.130859,0.295563,0.423630,0.374275,0.908691,0.588066,0.440788,0.467231</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>0.145690,0.229835,0.145675,0.276515,0.499696,0.623478,0.613101,0.595635,0.547813,0.599840,0.650764,0.679035,0.553451,0.303186,0.157636,0.009652,0.128963,0.290765,0.416385,0.367983,0.888695,0.577215,0.433847,0.459512</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>0.4247653238735712</v>
+      </c>
       <c r="K56" t="inlineStr">
         <is>
           <t>101.501205,101.323380,101.436447,101.582092,101.580559,101.501740,101.384415,101.425232,101.341553,101.445480,101.459808,101.390213,101.219254,101.427368,101.407349,101.144073,101.386475,101.279076,101.290939,101.238297,101.306732,101.121277,101.270401,101.312614</t>
@@ -5962,6 +6018,49 @@
       <c r="M56" t="inlineStr">
         <is>
           <t>100.863075,100.683830,100.658966,100.654343,100.527344,100.432709,100.395866,100.281731,100.327148,100.154861,100.090981,100.099724,100.011108,99.879738,100.116409,99.888382,99.825989,99.707108,99.626656,99.631973,99.668816,99.486633,99.403824,99.386078</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-09-13 04:31:04</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>24</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>101.638718,101.654129,101.622101,101.694626,101.671326,101.733749,101.780540,101.700241,101.695145,101.768417,101.765869,101.738602,101.759285,101.749794,101.768768,101.778397,101.747322,101.773956,101.709885,101.853241,101.835083,101.807999,101.796043,101.769577</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>101.664841,101.538467,101.627205,101.826088,101.993713,101.736801,101.794792,101.670471,101.640717,101.817078,101.844360,101.869232,101.780167,101.942505,101.719376,101.694122,101.822723,101.850830,101.902985,101.826202,101.803642,101.646637,101.848396,101.757111</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>100.902832,100.927521,100.743393,100.795059,100.648010,100.648460,100.706535,100.455139,100.289902,100.265343,100.257629,100.041405,100.131653,99.994034,99.974472,99.879044,99.810562,99.768929,99.498947,99.540962,99.480751,99.371307,99.408768,99.334991</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>101.201553,101.176430,101.077904,101.089561,101.036499,101.034683,101.066780,100.957840,100.905548,100.879868,100.748489,100.776886,100.761482,100.626282,100.677917,100.583565,100.520485,100.479294,100.410690,100.470398,100.427612,100.326355,100.353645,100.323029</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J57"/>
+  <dimension ref="A1:J58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2583,6 +2583,44 @@
       </c>
       <c r="F57" t="n">
         <v>101.7695770263672</v>
+      </c>
+      <c r="G57" t="n">
+        <v>101.0500030517578</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.7195739746093892</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.7120969350597876</v>
+      </c>
+      <c r="J57" t="n">
+        <v>1.266337914184963</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-09-14 04:37:24</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>24</v>
+      </c>
+      <c r="F58" t="n">
+        <v>101.0026245117188</v>
       </c>
     </row>
   </sheetData>
@@ -2596,7 +2634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M57"/>
+  <dimension ref="A1:M58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6048,6 +6086,24 @@
           <t>101.638718,101.654129,101.622101,101.694626,101.671326,101.733749,101.780540,101.700241,101.695145,101.768417,101.765869,101.738602,101.759285,101.749794,101.768768,101.778397,101.747322,101.773956,101.709885,101.853241,101.835083,101.807999,101.796043,101.769577</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>101.790001,101.220001,100.690002,99.970001,99.830002,99.519997,99.790001,99.690002,100.080002,100.639999,100.209999,100.790001,100.970001,101.180000,100.919998,101.440002,101.320000,99.690002,99.250000,99.629997,100.120003,100.959999,100.940002,101.050003</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>0.151283,0.434128,0.932099,1.724625,1.841324,2.213752,1.990539,2.010239,1.615143,1.128418,1.555870,0.948601,0.789284,0.569794,0.848770,0.338395,0.427322,2.083954,2.459885,2.223244,1.715080,0.848000,0.856041,0.719574</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>0.148623,0.428895,0.925711,1.725142,1.844460,2.224430,1.994728,2.016490,1.613852,1.121242,1.552609,0.941166,0.781701,0.563149,0.841032,0.333591,0.421755,2.090434,2.478474,2.231500,1.713025,0.839937,0.848069,0.712097</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>1.266337914184963</v>
+      </c>
       <c r="K57" t="inlineStr">
         <is>
           <t>101.664841,101.538467,101.627205,101.826088,101.993713,101.736801,101.794792,101.670471,101.640717,101.817078,101.844360,101.869232,101.780167,101.942505,101.719376,101.694122,101.822723,101.850830,101.902985,101.826202,101.803642,101.646637,101.848396,101.757111</t>
@@ -6061,6 +6117,49 @@
       <c r="M57" t="inlineStr">
         <is>
           <t>101.201553,101.176430,101.077904,101.089561,101.036499,101.034683,101.066780,100.957840,100.905548,100.879868,100.748489,100.776886,100.761482,100.626282,100.677917,100.583565,100.520485,100.479294,100.410690,100.470398,100.427612,100.326355,100.353645,100.323029</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-09-14 04:37:24</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>24</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>100.933723,100.945251,100.913559,100.971527,100.947304,100.998245,100.984741,100.976929,101.035172,101.000999,101.015915,101.029312,101.076004,101.043869,101.077301,101.104858,101.046539,101.046661,101.028397,101.113739,101.044281,101.019455,101.030258,101.002625</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>100.866417,100.876541,100.895920,101.042824,101.147217,100.932327,101.156540,100.994003,101.020996,101.052460,101.205124,101.022377,101.041290,101.159760,101.160416,101.063141,101.267593,101.356293,101.257919,101.130966,101.089638,100.918121,101.209785,101.100311</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>100.120911,100.016693,99.803635,99.836853,99.689575,99.656212,99.626022,99.445351,99.356094,99.232727,99.233673,99.010948,99.022102,98.946274,98.992996,98.938232,98.796707,98.780609,98.484306,98.486916,98.435143,98.389671,98.387413,98.329224</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>100.441757,100.371994,100.218979,100.248352,100.175293,100.079285,100.106689,100.081528,100.082916,99.913208,99.765198,99.857315,99.810608,99.683342,99.821968,99.795013,99.623787,99.574257,99.466812,99.510612,99.447029,99.370071,99.386093,99.320663</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J58"/>
+  <dimension ref="A1:J59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2621,6 +2621,44 @@
       </c>
       <c r="F58" t="n">
         <v>101.0026245117188</v>
+      </c>
+      <c r="G58" t="n">
+        <v>101.1999969482422</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.1973724365233807</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.1950320577819039</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1.084252005237763</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-09-15 04:37:52</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>24</v>
+      </c>
+      <c r="F59" t="n">
+        <v>100.9935836791992</v>
       </c>
     </row>
   </sheetData>
@@ -2634,7 +2672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M58"/>
+  <dimension ref="A1:M59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6147,6 +6185,24 @@
           <t>100.933723,100.945251,100.913559,100.971527,100.947304,100.998245,100.984741,100.976929,101.035172,101.000999,101.015915,101.029312,101.076004,101.043869,101.077301,101.104858,101.046539,101.046661,101.028397,101.113739,101.044281,101.019455,101.030258,101.002625</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>101.050003,101.500000,101.559998,101.459999,101.900002,101.730003,101.309998,101.330002,101.309998,101.610001,101.949997,102.589996,103.040001,103.610001,103.260002,103.980003,103.180000,102.849998,102.559998,102.459999,102.239998,101.940002,101.489998,101.199997</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>0.116280,0.554749,0.646439,0.488472,0.952698,0.731758,0.325257,0.353073,0.274826,0.609002,0.934082,1.560684,1.963997,2.566132,2.182701,2.875145,2.133461,1.803337,1.531601,1.346260,1.195717,0.920547,0.459740,0.197372</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>0.115072,0.546551,0.636509,0.481443,0.934934,0.719314,0.321051,0.348439,0.271272,0.599352,0.916216,1.521283,1.906053,2.476722,2.113791,2.765095,2.067708,1.753367,1.493370,1.313937,1.169520,0.903029,0.452990,0.195032</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>1.084252005237763</v>
+      </c>
       <c r="K58" t="inlineStr">
         <is>
           <t>100.866417,100.876541,100.895920,101.042824,101.147217,100.932327,101.156540,100.994003,101.020996,101.052460,101.205124,101.022377,101.041290,101.159760,101.160416,101.063141,101.267593,101.356293,101.257919,101.130966,101.089638,100.918121,101.209785,101.100311</t>
@@ -6160,6 +6216,49 @@
       <c r="M58" t="inlineStr">
         <is>
           <t>100.441757,100.371994,100.218979,100.248352,100.175293,100.079285,100.106689,100.081528,100.082916,99.913208,99.765198,99.857315,99.810608,99.683342,99.821968,99.795013,99.623787,99.574257,99.466812,99.510612,99.447029,99.370071,99.386093,99.320663</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-09-15 04:37:52</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>24</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>101.203316,101.165848,101.115509,101.119247,101.037262,101.087143,101.068611,101.064285,101.078125,101.087105,101.104874,101.172226,101.242096,101.198105,101.275330,101.306625,101.220467,101.185524,101.130516,101.205612,101.114319,101.034637,101.008842,100.993584</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>101.173248,101.153290,101.166000,101.162483,101.117256,101.232117,101.211563,100.944260,101.103989,101.077423,101.195213,101.262268,101.076958,101.341370,101.317062,101.255173,101.276405,101.290710,101.212051,101.124825,100.997223,100.809311,101.117905,100.956360</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>100.330299,100.166840,99.953094,99.916809,99.622635,99.614975,99.490265,99.323410,99.299873,99.185173,99.174446,98.987854,99.030571,98.992950,99.079727,98.975334,98.826157,98.688858,98.323624,98.325920,98.253830,98.030342,98.080750,97.984634</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>100.691742,100.568069,100.405807,100.362167,100.190903,100.122299,100.140823,100.063171,100.138779,99.897598,99.814438,99.872299,99.964508,99.817513,99.935455,99.949760,99.850525,99.587311,99.532028,99.520012,99.380493,99.223740,99.182770,99.112015</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J59"/>
+  <dimension ref="A1:J60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2659,6 +2659,44 @@
       </c>
       <c r="F59" t="n">
         <v>100.9935836791992</v>
+      </c>
+      <c r="G59" t="n">
+        <v>97.26000213623047</v>
+      </c>
+      <c r="H59" t="n">
+        <v>3.733581542968736</v>
+      </c>
+      <c r="I59" t="n">
+        <v>3.838763583141989</v>
+      </c>
+      <c r="J59" t="n">
+        <v>2.307669203444075</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-09-16 04:33:07</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>24</v>
+      </c>
+      <c r="F60" t="n">
+        <v>97.1314697265625</v>
       </c>
     </row>
   </sheetData>
@@ -2672,7 +2710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M59"/>
+  <dimension ref="A1:M60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6246,6 +6284,24 @@
           <t>101.203316,101.165848,101.115509,101.119247,101.037262,101.087143,101.068611,101.064285,101.078125,101.087105,101.104874,101.172226,101.242096,101.198105,101.275330,101.306625,101.220467,101.185524,101.130516,101.205612,101.114319,101.034637,101.008842,100.993584</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>101.309998,100.849998,100.410004,100.620003,100.790001,100.930000,100.820000,100.959999,100.500000,98.800003,99.320000,99.040001,100.169998,98.150002,97.809998,97.360001,96.559998,97.080002,96.830002,97.029999,96.419998,97.180000,97.190002,97.260002</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>0.106682,0.315850,0.705505,0.499244,0.247261,0.157143,0.248611,0.104286,0.578125,2.287102,1.784874,2.132225,1.072098,3.048103,3.465332,3.946624,4.660469,4.105522,4.300514,4.175613,4.694321,3.854637,3.818840,3.733582</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>0.105302,0.313187,0.702625,0.496168,0.245323,0.155695,0.246589,0.103294,0.575249,2.314880,1.797095,2.152893,1.070278,3.105556,3.542923,4.053640,4.826501,4.229009,4.441303,4.303425,4.868617,3.966492,3.929251,3.838764</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>2.307669203444075</v>
+      </c>
       <c r="K59" t="inlineStr">
         <is>
           <t>101.173248,101.153290,101.166000,101.162483,101.117256,101.232117,101.211563,100.944260,101.103989,101.077423,101.195213,101.262268,101.076958,101.341370,101.317062,101.255173,101.276405,101.290710,101.212051,101.124825,100.997223,100.809311,101.117905,100.956360</t>
@@ -6259,6 +6315,49 @@
       <c r="M59" t="inlineStr">
         <is>
           <t>100.691742,100.568069,100.405807,100.362167,100.190903,100.122299,100.140823,100.063171,100.138779,99.897598,99.814438,99.872299,99.964508,99.817513,99.935455,99.949760,99.850525,99.587311,99.532028,99.520012,99.380493,99.223740,99.182770,99.112015</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-09-16 04:33:07</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>24</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>97.256752,97.249817,97.267471,97.257011,97.278160,97.247787,97.290207,97.235062,97.266586,97.269112,97.238319,97.289391,97.317474,97.302345,97.303871,97.261978,97.241997,97.219650,97.210190,97.197769,97.254524,97.192276,97.113571,97.131470</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>97.262619,97.394905,97.181122,97.361031,97.406471,97.520065,97.492813,97.093506,97.480446,97.419128,97.455856,97.448669,97.577255,97.528366,97.522873,97.167679,97.395805,97.494545,97.608261,97.297073,97.211670,97.051132,97.325974,97.368332</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>96.436432,96.200150,96.048630,96.010460,95.831451,95.690880,95.679955,95.447990,95.365044,95.134003,95.070442,94.961922,94.900970,94.819046,94.764412,94.548248,94.462822,94.342224,93.989426,93.899178,94.012390,93.850548,93.822372,93.831871</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>96.799194,96.636284,96.542839,96.420624,96.379768,96.265923,96.289047,96.131783,96.234192,95.930580,95.774223,95.874809,95.836212,95.733368,95.761726,95.625778,95.650780,95.302750,95.295685,95.204987,95.272598,95.110596,95.085007,95.095955</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J60"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2697,6 +2697,44 @@
       </c>
       <c r="F60" t="n">
         <v>97.1314697265625</v>
+      </c>
+      <c r="G60" t="n">
+        <v>99.33000183105469</v>
+      </c>
+      <c r="H60" t="n">
+        <v>2.198532104492188</v>
+      </c>
+      <c r="I60" t="n">
+        <v>2.21336158659451</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0.7773803729140928</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-09-17 04:38:32</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>24</v>
+      </c>
+      <c r="F61" t="n">
+        <v>99.01626586914062</v>
       </c>
     </row>
   </sheetData>
@@ -2710,7 +2748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M60"/>
+  <dimension ref="A1:M61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6345,6 +6383,24 @@
           <t>97.256752,97.249817,97.267471,97.257011,97.278160,97.247787,97.290207,97.235062,97.266586,97.269112,97.238319,97.289391,97.317474,97.302345,97.303871,97.261978,97.241997,97.219650,97.210190,97.197769,97.254524,97.192276,97.113571,97.131470</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>97.160004,97.300003,96.900002,96.970001,97.209999,97.150002,97.930000,97.489998,97.099998,96.959999,97.050003,97.150002,97.129997,97.680000,97.989998,98.629997,98.309998,97.400002,98.699997,98.620003,99.169998,99.290001,99.879997,99.330002</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>0.096748,0.050186,0.367469,0.287010,0.068161,0.097785,0.639793,0.254936,0.166588,0.309113,0.188316,0.139389,0.187477,0.377655,0.686127,1.368019,1.068001,0.180352,1.489807,1.422234,1.915474,2.097725,2.766426,2.198532</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>0.099576,0.051579,0.379225,0.295978,0.070117,0.100654,0.653317,0.261500,0.171563,0.318805,0.194040,0.143479,0.193016,0.386625,0.700201,1.387021,1.086360,0.185166,1.509430,1.442135,1.931506,2.112725,2.769750,2.213361</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>0.7773803729140928</v>
+      </c>
       <c r="K60" t="inlineStr">
         <is>
           <t>97.262619,97.394905,97.181122,97.361031,97.406471,97.520065,97.492813,97.093506,97.480446,97.419128,97.455856,97.448669,97.577255,97.528366,97.522873,97.167679,97.395805,97.494545,97.608261,97.297073,97.211670,97.051132,97.325974,97.368332</t>
@@ -6358,6 +6414,49 @@
       <c r="M60" t="inlineStr">
         <is>
           <t>96.799194,96.636284,96.542839,96.420624,96.379768,96.265923,96.289047,96.131783,96.234192,95.930580,95.774223,95.874809,95.836212,95.733368,95.761726,95.625778,95.650780,95.302750,95.295685,95.204987,95.272598,95.110596,95.085007,95.095955</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-09-17 04:38:32</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>24</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>99.365753,99.415901,99.444221,99.451324,99.532021,99.521851,99.552597,99.515518,99.509727,99.455750,99.481049,99.521561,99.428535,99.405746,99.385452,99.316254,99.293640,99.215240,99.211502,99.184074,99.089722,99.105553,99.026535,99.016266</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>99.382812,99.451691,99.387459,99.428734,99.439224,99.596222,99.546188,99.592155,99.485542,99.654022,99.571457,99.521637,99.571625,99.433594,99.512566,99.356392,99.266251,99.186539,99.271698,99.249390,99.037010,99.086052,98.956047,99.100334</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>98.562988,98.427284,98.197632,98.059982,97.991615,97.841377,97.794395,97.614532,97.572449,97.315109,97.328529,97.080399,96.915939,96.829361,96.791328,96.573448,96.458122,96.371696,96.094742,95.948059,95.955147,95.935005,95.841187,95.849754</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>98.835335,98.817047,98.656830,98.549385,98.567276,98.428047,98.477448,98.386185,98.340691,98.007057,97.926010,97.974152,97.757835,97.681366,97.735909,97.601646,97.542564,97.305870,97.272018,97.159309,97.110077,97.126587,97.074104,97.033012</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:J62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2735,6 +2735,44 @@
       </c>
       <c r="F61" t="n">
         <v>99.01626586914062</v>
+      </c>
+      <c r="G61" t="n">
+        <v>105.0299987792969</v>
+      </c>
+      <c r="H61" t="n">
+        <v>6.01373291015625</v>
+      </c>
+      <c r="I61" t="n">
+        <v>5.725728820385034</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1.783823613580849</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-09-18 04:23:47</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>24</v>
+      </c>
+      <c r="F62" t="n">
+        <v>104.0468521118164</v>
       </c>
     </row>
   </sheetData>
@@ -2748,7 +2786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M61"/>
+  <dimension ref="A1:M62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6444,6 +6482,24 @@
           <t>99.365753,99.415901,99.444221,99.451324,99.532021,99.521851,99.552597,99.515518,99.509727,99.455750,99.481049,99.521561,99.428535,99.405746,99.385452,99.316254,99.293640,99.215240,99.211502,99.184074,99.089722,99.105553,99.026535,99.016266</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>99.459999,99.650002,99.940002,100.239998,100.160004,99.760002,100.019997,100.639999,100.639999,100.959999,101.199997,101.309998,101.440002,100.769997,100.900002,101.220001,101.070000,101.370003,101.540001,101.330002,102.410004,102.669998,104.480003,105.029999</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>0.094246,0.234101,0.495781,0.788674,0.627983,0.238151,0.467400,1.124481,1.130272,1.504249,1.718948,1.788437,2.011467,1.364251,1.514550,1.903747,1.776360,2.154763,2.328499,2.145928,3.320282,3.564445,5.453468,6.013733</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>0.094758,0.234923,0.496079,0.786786,0.626979,0.238724,0.467306,1.117330,1.123085,1.489946,1.698565,1.765311,1.982913,1.353826,1.501040,1.880801,1.757554,2.125641,2.293184,2.117762,3.242146,3.471750,5.219629,5.725729</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>1.783823613580849</v>
+      </c>
       <c r="K61" t="inlineStr">
         <is>
           <t>99.382812,99.451691,99.387459,99.428734,99.439224,99.596222,99.546188,99.592155,99.485542,99.654022,99.571457,99.521637,99.571625,99.433594,99.512566,99.356392,99.266251,99.186539,99.271698,99.249390,99.037010,99.086052,98.956047,99.100334</t>
@@ -6457,6 +6513,49 @@
       <c r="M61" t="inlineStr">
         <is>
           <t>98.835335,98.817047,98.656830,98.549385,98.567276,98.428047,98.477448,98.386185,98.340691,98.007057,97.926010,97.974152,97.757835,97.681366,97.735909,97.601646,97.542564,97.305870,97.272018,97.159309,97.110077,97.126587,97.074104,97.033012</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-09-18 04:23:47</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>24</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>104.951355,104.978844,104.899849,104.901459,104.842331,104.803207,104.773392,104.708504,104.664879,104.662903,104.636536,104.609283,104.539421,104.427231,104.401970,104.284683,104.284645,104.211754,104.167053,104.121635,104.060638,104.062668,104.046783,104.046852</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>104.934273,104.821136,104.855255,104.805588,104.771957,104.757591,104.692047,104.776581,104.511520,104.637039,104.580254,104.522430,104.588074,104.390411,104.392639,104.250778,104.277107,104.303574,104.169403,104.088814,103.930099,104.129463,103.991280,103.881752</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>103.648071,103.364082,102.983383,102.784317,102.563721,102.431969,102.271576,101.998802,101.983383,101.814224,101.824425,101.528290,101.585693,101.312546,101.219528,101.033562,100.987465,100.876282,100.624046,100.343445,100.401230,100.297943,100.324280,100.349152</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>104.120102,103.969299,103.655220,103.583382,103.372604,103.240120,103.248627,103.014420,102.967728,102.775955,102.692581,102.669098,102.543976,102.333252,102.323975,102.180695,102.146355,101.983322,101.863068,101.699982,101.639839,101.619659,101.638000,101.628845</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J62"/>
+  <dimension ref="A1:J63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2773,6 +2773,44 @@
       </c>
       <c r="F62" t="n">
         <v>104.0468521118164</v>
+      </c>
+      <c r="G62" t="n">
+        <v>113.1900024414062</v>
+      </c>
+      <c r="H62" t="n">
+        <v>9.143150329589844</v>
+      </c>
+      <c r="I62" t="n">
+        <v>8.077701327308365</v>
+      </c>
+      <c r="J62" t="n">
+        <v>5.152678027758084</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-09-19 04:20:42</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>24</v>
+      </c>
+      <c r="F63" t="n">
+        <v>112.6486358642578</v>
       </c>
     </row>
   </sheetData>
@@ -2786,7 +2824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M62"/>
+  <dimension ref="A1:M63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6543,6 +6581,24 @@
           <t>104.951355,104.978844,104.899849,104.901459,104.842331,104.803207,104.773392,104.708504,104.664879,104.662903,104.636536,104.609283,104.539421,104.427231,104.401970,104.284683,104.284645,104.211754,104.167053,104.121635,104.060638,104.062668,104.046783,104.046852</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>105.279999,105.480003,105.690002,106.279999,106.330002,106.190002,105.639999,105.690002,108.470001,110.709999,111.129997,111.660004,112.570000,112.129997,114.330002,113.510002,113.169998,113.110001,112.699997,113.629997,113.389999,113.580002,113.209999,113.190002</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>0.328644,0.501159,0.790153,1.378540,1.487671,1.386795,0.866607,0.981498,3.805122,6.047096,6.493461,7.050721,8.030579,7.702766,9.928032,9.225319,8.885353,8.898247,8.532944,9.508362,9.329361,9.517334,9.163216,9.143150</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>0.312162,0.475123,0.747614,1.297083,1.399107,1.305957,0.820340,0.928658,3.507995,5.462105,5.843122,6.314455,7.133853,6.869497,8.683663,8.127318,7.851333,7.866896,7.571379,8.367828,8.227676,8.379410,8.093999,8.077701</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>5.152678027758084</v>
+      </c>
       <c r="K62" t="inlineStr">
         <is>
           <t>104.934273,104.821136,104.855255,104.805588,104.771957,104.757591,104.692047,104.776581,104.511520,104.637039,104.580254,104.522430,104.588074,104.390411,104.392639,104.250778,104.277107,104.303574,104.169403,104.088814,103.930099,104.129463,103.991280,103.881752</t>
@@ -6556,6 +6612,49 @@
       <c r="M62" t="inlineStr">
         <is>
           <t>104.120102,103.969299,103.655220,103.583382,103.372604,103.240120,103.248627,103.014420,102.967728,102.775955,102.692581,102.669098,102.543976,102.333252,102.323975,102.180695,102.146355,101.983322,101.863068,101.699982,101.639839,101.619659,101.638000,101.628845</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-09-19 04:20:42</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>24</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>113.161903,113.223610,113.254570,113.303642,113.293640,113.227203,113.263367,113.200645,113.172668,113.107574,113.130920,113.039749,113.012207,112.861580,112.919022,112.861694,112.948059,112.846909,112.862587,112.674194,112.720795,112.714569,112.657196,112.648636</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>112.836044,112.981857,113.009834,113.060333,112.943298,112.889961,112.655632,112.876999,112.616409,112.796944,112.713158,112.373634,112.215256,112.364059,112.254990,112.297569,112.209885,112.085297,112.044304,112.121635,111.925171,112.279739,111.774017,111.783768</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>111.884399,111.683838,111.367401,111.145660,110.915222,110.601074,110.294022,109.995148,109.984543,109.712280,109.571960,109.167786,109.296883,108.813202,108.541000,108.477295,108.344482,108.092186,107.731400,107.144394,107.139877,107.014824,106.825043,107.001328</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>112.454849,112.383949,112.138901,112.173935,111.900070,111.675713,111.682167,111.430679,111.392990,111.166397,110.977982,110.927773,110.731171,110.461060,110.290230,110.310349,110.268425,109.956596,109.830223,109.526947,109.452423,109.257339,109.191879,109.198853</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J63"/>
+  <dimension ref="A1:J64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2811,6 +2811,44 @@
       </c>
       <c r="F63" t="n">
         <v>112.6486358642578</v>
+      </c>
+      <c r="G63" t="n">
+        <v>109.0699996948242</v>
+      </c>
+      <c r="H63" t="n">
+        <v>3.57863616943358</v>
+      </c>
+      <c r="I63" t="n">
+        <v>3.281045364854254</v>
+      </c>
+      <c r="J63" t="n">
+        <v>1.78677002641767</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-09-20 04:39:44</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>24</v>
+      </c>
+      <c r="F64" t="n">
+        <v>108.2198028564453</v>
       </c>
     </row>
   </sheetData>
@@ -2824,7 +2862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M63"/>
+  <dimension ref="A1:M64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6642,6 +6680,24 @@
           <t>113.161903,113.223610,113.254570,113.303642,113.293640,113.227203,113.263367,113.200645,113.172668,113.107574,113.130920,113.039749,113.012207,112.861580,112.919022,112.861694,112.948059,112.846909,112.862587,112.674194,112.720795,112.714569,112.657196,112.648636</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>111.900002,111.790001,111.559998,112.199997,111.790001,111.580002,111.849998,111.730003,111.580002,111.750000,111.589996,111.959999,111.370003,111.120003,111.139999,111.070000,110.500000,110.620003,111.019997,110.930000,110.120003,107.620003,108.860001,109.070000</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>1.261901,1.433609,1.694572,1.103645,1.503639,1.647201,1.413369,1.470642,1.592666,1.357574,1.540924,1.079750,1.642204,1.741577,1.779023,1.791694,2.448059,2.226906,1.842590,1.744194,2.600792,5.094566,3.797195,3.578636</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1.127705,1.282413,1.518979,0.983641,1.345057,1.476251,1.263629,1.316246,1.427376,1.214831,1.380880,0.964407,1.474548,1.567294,1.600704,1.613122,2.215438,2.013114,1.659692,1.572337,2.361780,4.733847,3.488146,3.281045</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>1.78677002641767</v>
+      </c>
       <c r="K63" t="inlineStr">
         <is>
           <t>112.836044,112.981857,113.009834,113.060333,112.943298,112.889961,112.655632,112.876999,112.616409,112.796944,112.713158,112.373634,112.215256,112.364059,112.254990,112.297569,112.209885,112.085297,112.044304,112.121635,111.925171,112.279739,111.774017,111.783768</t>
@@ -6655,6 +6711,49 @@
       <c r="M63" t="inlineStr">
         <is>
           <t>112.454849,112.383949,112.138901,112.173935,111.900070,111.675713,111.682167,111.430679,111.392990,111.166397,110.977982,110.927773,110.731171,110.461060,110.290230,110.310349,110.268425,109.956596,109.830223,109.526947,109.452423,109.257339,109.191879,109.198853</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-09-20 04:39:44</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>24</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>109.002853,108.925201,108.942047,108.887741,108.830765,108.755081,108.751694,108.644852,108.662033,108.624542,108.607422,108.594131,108.570602,108.467072,108.424561,108.335808,108.325745,108.378937,108.264664,108.237244,108.204880,108.214409,108.198273,108.219803</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>108.822220,108.896042,108.876862,108.809525,108.812561,108.694656,108.619011,108.507828,108.594803,108.671829,108.602707,108.483765,108.387589,108.366135,108.238029,108.359039,108.237427,108.206055,108.180626,108.181778,108.140869,108.130432,108.086700,108.281998</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>108.044678,107.783691,107.519539,107.246033,107.037857,106.767700,106.592789,106.333603,106.390289,106.163292,106.046333,105.935966,105.947311,105.586540,105.324562,105.135101,104.985168,104.950668,104.495293,104.293213,104.242844,104.119156,104.067413,104.019997</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>108.457428,108.271362,108.090195,107.920547,107.700974,107.524727,107.454514,107.215652,107.307076,107.081070,106.992813,107.051102,106.832993,106.647858,106.485718,106.353134,106.241135,106.210846,105.971573,105.940201,105.828217,105.726746,105.697708,105.600143</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J64"/>
+  <dimension ref="A1:J65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2849,6 +2849,44 @@
       </c>
       <c r="F64" t="n">
         <v>108.2198028564453</v>
+      </c>
+      <c r="G64" t="n">
+        <v>111.3899993896484</v>
+      </c>
+      <c r="H64" t="n">
+        <v>3.170196533203139</v>
+      </c>
+      <c r="I64" t="n">
+        <v>2.846033351803527</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1.367358842569277</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-09-21 04:37:40</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>24</v>
+      </c>
+      <c r="F65" t="n">
+        <v>111.0229187011719</v>
       </c>
     </row>
   </sheetData>
@@ -2862,7 +2900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M64"/>
+  <dimension ref="A1:M65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6741,6 +6779,24 @@
           <t>109.002853,108.925201,108.942047,108.887741,108.830765,108.755081,108.751694,108.644852,108.662033,108.624542,108.607422,108.594131,108.570602,108.467072,108.424561,108.335808,108.325745,108.378937,108.264664,108.237244,108.204880,108.214409,108.198273,108.219803</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>108.720001,108.410004,108.430000,108.029999,108.250000,107.980003,108.410004,108.349998,108.199997,108.110001,108.779999,110.309998,109.889999,109.370003,110.419998,110.099998,109.860001,111.019997,111.139999,112.279999,110.930000,111.190002,111.519997,111.389999</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>0.282852,0.515197,0.512047,0.857742,0.580765,0.775078,0.341690,0.294854,0.462036,0.514541,0.172577,1.715867,1.319397,0.902931,1.995437,1.764190,1.534256,2.641060,2.875335,4.042755,2.725120,2.975593,3.321724,3.170196</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>0.260165,0.475230,0.472237,0.793985,0.536503,0.717797,0.315183,0.272131,0.427020,0.475942,0.158648,1.555495,1.200653,0.825574,1.807134,1.602353,1.396555,2.378904,2.587129,3.600601,2.456613,2.676134,2.978590,2.846033</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>1.367358842569277</v>
+      </c>
       <c r="K64" t="inlineStr">
         <is>
           <t>108.822220,108.896042,108.876862,108.809525,108.812561,108.694656,108.619011,108.507828,108.594803,108.671829,108.602707,108.483765,108.387589,108.366135,108.238029,108.359039,108.237427,108.206055,108.180626,108.181778,108.140869,108.130432,108.086700,108.281998</t>
@@ -6754,6 +6810,49 @@
       <c r="M64" t="inlineStr">
         <is>
           <t>108.457428,108.271362,108.090195,107.920547,107.700974,107.524727,107.454514,107.215652,107.307076,107.081070,106.992813,107.051102,106.832993,106.647858,106.485718,106.353134,106.241135,106.210846,105.971573,105.940201,105.828217,105.726746,105.697708,105.600143</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-09-21 04:37:40</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>24</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>111.357582,111.442963,111.463867,111.498642,111.533157,111.557571,111.516769,111.501801,111.485542,111.413940,111.425217,111.402786,111.346573,111.278336,111.281616,111.283386,111.271118,111.236038,111.146149,111.064476,111.094894,111.021812,111.044846,111.022919</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>111.255981,111.325752,111.454544,111.440834,111.451118,111.480537,111.205353,111.465042,111.189163,111.405151,111.325378,111.109711,111.015839,111.051826,111.009109,111.233505,110.839622,110.908272,110.871979,110.784912,110.779694,111.054329,110.887047,110.652145</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>110.468918,110.337616,110.074753,109.946732,109.789291,109.653969,109.478836,109.268860,109.175995,108.902946,108.735474,108.610603,108.438263,108.137383,107.962326,107.919579,107.748795,107.663712,107.274719,106.896591,106.984337,106.738976,106.721107,106.684891</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>110.819099,110.811150,110.621628,110.574051,110.448807,110.357857,110.303642,110.121368,110.088791,109.879745,109.751884,109.778969,109.579018,109.333038,109.203545,109.261230,109.097427,108.987930,108.729858,108.640556,108.602402,108.344948,108.403961,108.324127</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J65"/>
+  <dimension ref="A1:J66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2887,6 +2887,44 @@
       </c>
       <c r="F65" t="n">
         <v>111.0229187011719</v>
+      </c>
+      <c r="G65" t="n">
+        <v>116.5400009155273</v>
+      </c>
+      <c r="H65" t="n">
+        <v>5.51708221435544</v>
+      </c>
+      <c r="I65" t="n">
+        <v>4.734067419781842</v>
+      </c>
+      <c r="J65" t="n">
+        <v>4.695439407946289</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-09-22 04:33:37</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>24</v>
+      </c>
+      <c r="F66" t="n">
+        <v>114.3772354125977</v>
       </c>
     </row>
   </sheetData>
@@ -2900,7 +2938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M65"/>
+  <dimension ref="A1:M66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6840,6 +6878,24 @@
           <t>111.357582,111.442963,111.463867,111.498642,111.533157,111.557571,111.516769,111.501801,111.485542,111.413940,111.425217,111.402786,111.346573,111.278336,111.281616,111.283386,111.271118,111.236038,111.146149,111.064476,111.094894,111.021812,111.044846,111.022919</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>111.739998,112.169998,112.080002,115.320000,115.940002,115.980003,116.769997,116.790001,118.010002,118.040001,117.919998,117.529999,117.190002,117.730003,118.339996,119.209999,119.110001,119.419998,118.900002,118.320000,117.559998,116.889999,116.779999,116.540001</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>0.382416,0.727035,0.616135,3.821358,4.406845,4.422432,5.253228,5.288200,6.524460,6.626061,6.494781,6.127213,5.843429,6.451667,7.058380,7.926613,7.838883,8.183960,7.753853,7.255524,6.465104,5.868187,5.735153,5.517082</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>0.342237,0.648155,0.549728,3.313699,3.800971,3.813099,4.498782,4.527956,5.528735,5.613403,5.507786,5.213318,4.986287,5.480054,5.964493,6.649285,6.581213,6.853090,6.521322,6.132119,5.499408,5.020265,4.911075,4.734067</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>4.695439407946289</v>
+      </c>
       <c r="K65" t="inlineStr">
         <is>
           <t>111.255981,111.325752,111.454544,111.440834,111.451118,111.480537,111.205353,111.465042,111.189163,111.405151,111.325378,111.109711,111.015839,111.051826,111.009109,111.233505,110.839622,110.908272,110.871979,110.784912,110.779694,111.054329,110.887047,110.652145</t>
@@ -6853,6 +6909,49 @@
       <c r="M65" t="inlineStr">
         <is>
           <t>110.819099,110.811150,110.621628,110.574051,110.448807,110.357857,110.303642,110.121368,110.088791,109.879745,109.751884,109.778969,109.579018,109.333038,109.203545,109.261230,109.097427,108.987930,108.729858,108.640556,108.602402,108.344948,108.403961,108.324127</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-09-22 04:33:37</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>24</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>116.502502,116.260941,116.176544,116.140594,115.973373,115.836044,115.767090,115.619476,115.547012,115.423752,115.295700,115.258133,115.045174,114.900139,114.989182,115.004349,114.980980,114.916641,114.850098,114.687187,114.652199,114.537338,114.429428,114.377235</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>116.207581,116.090149,116.076538,116.079979,115.905563,115.716469,115.373215,115.493835,115.133316,115.328735,115.180908,114.919746,114.640564,114.607529,114.770935,114.692085,114.736725,114.507675,114.559326,114.335907,114.312431,114.408508,114.031319,113.942734</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>115.414467,114.959763,114.545731,114.312195,113.881767,113.493484,113.211349,112.807022,112.661652,112.362083,112.081024,111.821472,111.615501,111.298019,111.101608,111.054054,110.860794,110.732986,110.315414,109.813446,109.807114,109.551659,109.386734,109.460449</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>115.872208,115.476395,115.149513,115.045944,114.695724,114.369781,114.249557,113.929893,113.806389,113.557053,113.289917,113.262283,112.881752,112.620903,112.544022,112.542633,112.417923,112.165421,112.016632,111.747055,111.640961,111.362823,111.299301,111.223373</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J66"/>
+  <dimension ref="A1:J67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2925,6 +2925,44 @@
       </c>
       <c r="F66" t="n">
         <v>114.3772354125977</v>
+      </c>
+      <c r="G66" t="n">
+        <v>119.4899978637695</v>
+      </c>
+      <c r="H66" t="n">
+        <v>5.112762451171832</v>
+      </c>
+      <c r="I66" t="n">
+        <v>4.278820439013556</v>
+      </c>
+      <c r="J66" t="n">
+        <v>2.127680946460533</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-09-23 04:30:02</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>24</v>
+      </c>
+      <c r="F67" t="n">
+        <v>119.6565399169922</v>
       </c>
     </row>
   </sheetData>
@@ -2938,7 +2976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M66"/>
+  <dimension ref="A1:M67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6939,6 +6977,24 @@
           <t>116.502502,116.260941,116.176544,116.140594,115.973373,115.836044,115.767090,115.619476,115.547012,115.423752,115.295700,115.258133,115.045174,114.900139,114.989182,115.004349,114.980980,114.916641,114.850098,114.687187,114.652199,114.537338,114.429428,114.377235</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>116.809998,116.510002,116.290001,117.489998,117.440002,116.839996,117.309998,117.419998,117.940002,116.900002,117.370003,117.459999,117.980003,118.160004,118.220001,118.019997,118.099998,118.470001,118.559998,118.809998,118.339996,118.489998,119.129997,119.489998</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>0.307496,0.249061,0.113457,1.349404,1.466629,1.003952,1.542908,1.800522,2.392990,1.476250,2.074303,2.201866,2.934829,3.259865,3.230819,3.015648,3.119018,3.553360,3.709900,4.122811,3.687797,3.952660,4.700569,5.112763</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>0.263244,0.213768,0.097564,1.148527,1.248833,0.859254,1.315240,1.533403,2.028990,1.262831,1.767319,1.874567,2.487565,2.758856,2.732887,2.555201,2.640998,2.999376,3.129133,3.470087,3.116273,3.335860,3.945748,4.278821</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>2.127680946460533</v>
+      </c>
       <c r="K66" t="inlineStr">
         <is>
           <t>116.207581,116.090149,116.076538,116.079979,115.905563,115.716469,115.373215,115.493835,115.133316,115.328735,115.180908,114.919746,114.640564,114.607529,114.770935,114.692085,114.736725,114.507675,114.559326,114.335907,114.312431,114.408508,114.031319,113.942734</t>
@@ -6952,6 +7008,49 @@
       <c r="M66" t="inlineStr">
         <is>
           <t>115.872208,115.476395,115.149513,115.045944,114.695724,114.369781,114.249557,113.929893,113.806389,113.557053,113.289917,113.262283,112.881752,112.620903,112.544022,112.542633,112.417923,112.165421,112.016632,111.747055,111.640961,111.362823,111.299301,111.223373</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-09-23 04:30:02</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>24</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>119.581039,119.565506,119.699875,119.774361,119.816566,119.877075,119.997604,119.908127,119.976044,119.950668,119.915100,119.891937,119.834358,119.779068,119.845963,119.857605,119.939346,119.837265,119.814316,119.796494,119.878403,119.730354,119.720123,119.656540</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>119.430176,119.429565,119.575401,119.683006,119.904099,119.731522,119.780540,119.788803,119.718628,119.779526,119.717438,119.560120,119.407867,119.573303,119.560852,119.636124,119.561768,119.469055,119.615334,119.360596,119.548035,119.478729,119.237297,119.150131</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>118.880432,118.613785,118.508240,118.506416,118.285828,118.144432,118.122261,117.802658,117.726486,117.518967,117.399658,117.109276,117.010529,116.741882,116.539856,116.545944,116.380463,116.223999,115.861115,115.452454,115.558876,115.168808,115.108841,115.105331</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>119.171280,118.994560,118.998611,119.024818,118.914139,118.827187,118.921524,118.655731,118.673752,118.488579,118.359512,118.291397,118.149643,117.866486,117.780182,117.859299,117.846642,117.582901,117.387390,117.275795,117.222908,116.907227,116.913956,116.835457</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J67"/>
+  <dimension ref="A1:J68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2963,6 +2963,44 @@
       </c>
       <c r="F67" t="n">
         <v>119.6565399169922</v>
+      </c>
+      <c r="G67" t="n">
+        <v>114.7900009155273</v>
+      </c>
+      <c r="H67" t="n">
+        <v>4.866539001464858</v>
+      </c>
+      <c r="I67" t="n">
+        <v>4.23951473355775</v>
+      </c>
+      <c r="J67" t="n">
+        <v>3.515240961251603</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:27:13</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>24</v>
+      </c>
+      <c r="F68" t="n">
+        <v>114.4287719726562</v>
       </c>
     </row>
   </sheetData>
@@ -2976,7 +3014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M67"/>
+  <dimension ref="A1:M68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7038,6 +7076,24 @@
           <t>119.581039,119.565506,119.699875,119.774361,119.816566,119.877075,119.997604,119.908127,119.976044,119.950668,119.915100,119.891937,119.834358,119.779068,119.845963,119.857605,119.939346,119.837265,119.814316,119.796494,119.878403,119.730354,119.720123,119.656540</t>
         </is>
       </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>118.379997,118.949997,117.900002,117.389999,117.379997,117.620003,117.080002,116.889999,116.779999,115.150002,113.870003,114.400002,114.540001,114.279999,114.510002,114.029999,114.699997,115.129997,114.900002,115.129997,114.699997,115.279999,114.690002,114.790001</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>1.201042,0.615509,1.799873,2.384362,2.436569,2.257072,2.917602,3.018128,3.196045,4.800666,6.045097,5.491935,5.294357,5.499069,5.335961,5.827606,5.239349,4.707268,4.914314,4.666497,5.178406,4.450355,5.030121,4.866539</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1.014565,0.517452,1.526610,2.031145,2.075796,1.918953,2.491973,2.582024,2.736809,4.169055,5.308771,4.800643,4.622278,4.811926,4.659821,5.110590,4.567872,4.088654,4.277036,4.053241,4.514739,3.860475,4.385840,4.239515</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>3.515240961251603</v>
+      </c>
       <c r="K67" t="inlineStr">
         <is>
           <t>119.430176,119.429565,119.575401,119.683006,119.904099,119.731522,119.780540,119.788803,119.718628,119.779526,119.717438,119.560120,119.407867,119.573303,119.560852,119.636124,119.561768,119.469055,119.615334,119.360596,119.548035,119.478729,119.237297,119.150131</t>
@@ -7051,6 +7107,49 @@
       <c r="M67" t="inlineStr">
         <is>
           <t>119.171280,118.994560,118.998611,119.024818,118.914139,118.827187,118.921524,118.655731,118.673752,118.488579,118.359512,118.291397,118.149643,117.866486,117.780182,117.859299,117.846642,117.582901,117.387390,117.275795,117.222908,116.907227,116.913956,116.835457</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:27:13</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>24</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>114.771088,114.630707,114.641251,114.623062,114.544846,114.556778,114.580353,114.570129,114.557953,114.490959,114.494530,114.523941,114.551559,114.554756,114.559242,114.611168,114.599899,114.630844,114.547928,114.502480,114.560730,114.483719,114.477692,114.428772</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>114.541931,114.716209,114.569489,114.586136,114.638840,114.591812,114.583435,114.522461,114.501076,114.527649,114.355743,114.342102,114.300537,114.524399,114.562584,114.606262,114.425201,114.497742,114.582642,114.352493,114.356812,114.396011,114.327057,114.261887</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>113.963928,113.618996,113.406921,113.304840,113.096855,112.913010,112.803726,112.645874,112.435455,112.158676,111.981049,111.870361,111.890633,111.704956,111.512787,111.588028,111.293076,111.315773,110.868942,110.680984,110.677078,110.458870,110.378128,110.356018</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>114.283569,114.025681,113.892670,113.803627,113.587982,113.497467,113.478470,113.342422,113.245659,112.997574,112.799820,112.885460,112.863251,112.648399,112.568413,112.669861,112.483505,112.400017,112.209999,112.114128,112.097733,111.873787,111.914795,111.819412</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J68"/>
+  <dimension ref="A1:J69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3001,6 +3001,44 @@
       </c>
       <c r="F68" t="n">
         <v>114.4287719726562</v>
+      </c>
+      <c r="G68" t="n">
+        <v>116.9000015258789</v>
+      </c>
+      <c r="H68" t="n">
+        <v>2.471229553222713</v>
+      </c>
+      <c r="I68" t="n">
+        <v>2.11396879466733</v>
+      </c>
+      <c r="J68" t="n">
+        <v>1.457029484783315</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-09-25 04:38:30</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>24</v>
+      </c>
+      <c r="F69" t="n">
+        <v>116.8141326904297</v>
       </c>
     </row>
   </sheetData>
@@ -3014,7 +3052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M68"/>
+  <dimension ref="A1:M69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7137,6 +7175,24 @@
           <t>114.771088,114.630707,114.641251,114.623062,114.544846,114.556778,114.580353,114.570129,114.557953,114.490959,114.494530,114.523941,114.551559,114.554756,114.559242,114.611168,114.599899,114.630844,114.547928,114.502480,114.560730,114.483719,114.477692,114.428772</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>114.820000,114.809998,115.510002,114.110001,113.099998,113.349998,113.330002,113.790001,114.949997,114.589996,116.260002,117.059998,116.739998,117.370003,117.290001,116.820000,116.839996,116.580002,117.019997,117.400002,117.459999,116.879997,116.849998,116.900002</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>0.048912,0.179291,0.868751,0.513061,1.444848,1.206780,1.250351,0.780128,0.392044,0.099037,1.765472,2.536057,2.188439,2.815247,2.730759,2.208832,2.240097,1.949158,2.472069,2.897522,2.899269,2.396278,2.372306,2.471230</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>0.042599,0.156163,0.752100,0.449620,1.277496,1.064649,1.103283,0.685586,0.341056,0.086428,1.518555,2.166459,1.874626,2.398608,2.328211,1.890799,1.917235,1.671949,2.112518,2.468076,2.468303,2.050204,2.030215,2.113969</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>1.457029484783315</v>
+      </c>
       <c r="K68" t="inlineStr">
         <is>
           <t>114.541931,114.716209,114.569489,114.586136,114.638840,114.591812,114.583435,114.522461,114.501076,114.527649,114.355743,114.342102,114.300537,114.524399,114.562584,114.606262,114.425201,114.497742,114.582642,114.352493,114.356812,114.396011,114.327057,114.261887</t>
@@ -7150,6 +7206,49 @@
       <c r="M68" t="inlineStr">
         <is>
           <t>114.283569,114.025681,113.892670,113.803627,113.587982,113.497467,113.478470,113.342422,113.245659,112.997574,112.799820,112.885460,112.863251,112.648399,112.568413,112.669861,112.483505,112.400017,112.209999,112.114128,112.097733,111.873787,111.914795,111.819412</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-09-25 04:38:30</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>24</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>116.859184,116.781906,116.776260,116.784355,116.695923,116.711670,116.815079,116.744774,116.870911,116.893562,116.882767,116.922348,116.921715,116.909355,116.941628,116.925011,116.946548,116.897705,116.825531,116.858841,116.784195,116.743271,116.815979,116.814133</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>116.572433,116.675903,116.814102,116.565353,116.589005,116.779938,116.558640,116.682083,116.574501,116.757370,116.593765,116.446114,116.587555,116.544212,116.642654,116.776520,116.469971,116.549210,116.528458,116.447830,116.418854,116.530617,116.482422,116.392754</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>115.882385,115.594818,115.254578,115.153061,114.777115,114.557983,114.506165,114.263733,114.168747,113.977516,113.736420,113.639145,113.583420,113.403328,113.288635,113.259926,113.101486,113.051651,112.679688,112.529251,112.421555,112.225449,112.245850,112.284691</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>116.297142,116.075104,115.838905,115.788185,115.507660,115.407562,115.353226,115.154373,115.227516,115.066544,114.867104,114.909286,114.833069,114.632034,114.542755,114.586639,114.494003,114.393585,114.220291,114.221008,114.025925,113.920410,114.025658,113.994797</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J69"/>
+  <dimension ref="A1:J70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3039,6 +3039,44 @@
       </c>
       <c r="F69" t="n">
         <v>116.8141326904297</v>
+      </c>
+      <c r="G69" t="n">
+        <v>120.5800018310547</v>
+      </c>
+      <c r="H69" t="n">
+        <v>3.765869140624986</v>
+      </c>
+      <c r="I69" t="n">
+        <v>3.123129112156895</v>
+      </c>
+      <c r="J69" t="n">
+        <v>2.853570330139593</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-09-26 04:42:21</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>24</v>
+      </c>
+      <c r="F70" t="n">
+        <v>120.5276184082031</v>
       </c>
     </row>
   </sheetData>
@@ -3052,7 +3090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M69"/>
+  <dimension ref="A1:M70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7236,6 +7274,24 @@
           <t>116.859184,116.781906,116.776260,116.784355,116.695923,116.711670,116.815079,116.744774,116.870911,116.893562,116.882767,116.922348,116.921715,116.909355,116.941628,116.925011,116.946548,116.897705,116.825531,116.858841,116.784195,116.743271,116.815979,116.814133</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>116.400002,116.250000,116.360001,117.290001,118.379997,119.160004,120.809998,120.699997,119.480003,120.419998,120.080002,120.849998,121.000000,121.919998,121.849998,121.559998,120.989998,122.180000,122.150002,121.529999,122.029999,121.589996,120.629997,120.580002</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>0.459182,0.531906,0.416259,0.505646,1.684074,2.448334,3.994919,3.955223,2.609092,3.526436,3.197235,3.927650,4.078285,5.010643,4.908370,4.634987,4.043450,5.282295,5.324471,4.671158,5.245804,4.846725,3.814018,3.765869</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>0.394487,0.457554,0.357734,0.431107,1.422600,2.054661,3.306778,3.276904,2.183706,2.928447,2.662587,3.250021,3.370483,4.109780,4.028207,3.812921,3.341970,4.323371,4.358961,3.843625,4.298782,3.986122,3.161749,3.123129</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>2.853570330139593</v>
+      </c>
       <c r="K69" t="inlineStr">
         <is>
           <t>116.572433,116.675903,116.814102,116.565353,116.589005,116.779938,116.558640,116.682083,116.574501,116.757370,116.593765,116.446114,116.587555,116.544212,116.642654,116.776520,116.469971,116.549210,116.528458,116.447830,116.418854,116.530617,116.482422,116.392754</t>
@@ -7249,6 +7305,49 @@
       <c r="M69" t="inlineStr">
         <is>
           <t>116.297142,116.075104,115.838905,115.788185,115.507660,115.407562,115.353226,115.154373,115.227516,115.066544,114.867104,114.909286,114.833069,114.632034,114.542755,114.586639,114.494003,114.393585,114.220291,114.221008,114.025925,113.920410,114.025658,113.994797</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-09-26 04:42:21</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>24</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>120.626633,120.550346,120.567551,120.603531,120.577927,120.699394,120.694771,120.629913,120.715866,120.811455,120.751320,120.844475,120.847900,120.797699,120.877182,120.841263,120.822357,120.779411,120.739388,120.778709,120.751083,120.655479,120.588989,120.527618</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>120.501465,120.560944,120.508514,120.276855,120.590485,120.617264,120.351067,120.462769,120.497200,120.463974,120.632217,120.570084,120.482819,120.491013,120.618759,120.599747,120.495895,120.489388,120.492783,120.251740,120.313690,120.375122,120.328949,120.025352</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>119.546242,119.397873,119.189354,119.082794,118.746521,118.555252,118.479706,118.277115,118.143143,118.019531,117.834274,117.713196,117.604462,117.479340,117.341736,117.318024,117.146248,116.993843,116.651703,116.404137,116.319656,116.099434,116.010300,116.017426</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>120.054169,119.897003,119.768127,119.741356,119.476250,119.445740,119.363235,119.165192,119.202026,119.080673,118.864471,118.936768,118.902451,118.720993,118.610138,118.661133,118.535492,118.376495,118.182724,118.133347,117.963440,117.821472,117.757523,117.737076</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J70"/>
+  <dimension ref="A1:J71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3077,6 +3077,44 @@
       </c>
       <c r="F70" t="n">
         <v>120.5276184082031</v>
+      </c>
+      <c r="G70" t="n">
+        <v>120.1399993896484</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0.3876190185546591</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.3226394377591926</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0.3132386395177948</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-09-27 05:02:20</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>24</v>
+      </c>
+      <c r="F71" t="n">
+        <v>118.8420791625977</v>
       </c>
     </row>
   </sheetData>
@@ -3090,7 +3128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M70"/>
+  <dimension ref="A1:M71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7335,6 +7373,24 @@
           <t>120.626633,120.550346,120.567551,120.603531,120.577927,120.699394,120.694771,120.629913,120.715866,120.811455,120.751320,120.844475,120.847900,120.797699,120.877182,120.841263,120.822357,120.779411,120.739388,120.778709,120.751083,120.655479,120.588989,120.527618</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>120.510002,120.209999,120.750000,120.680000,119.959999,120.620003,121.260002,121.059998,120.760002,120.949997,121.860001,121.620003,121.480003,121.040001,121.120003,120.339996,121.300003,121.120003,121.379997,120.800003,121.410004,121.129997,120.580002,120.139999</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>0.116631,0.340347,0.182449,0.076469,0.617928,0.079391,0.565231,0.430085,0.044136,0.138542,1.108681,0.775528,0.632103,0.242302,0.242821,0.501267,0.477646,0.340592,0.640609,0.021294,0.658921,0.474518,0.008987,0.387619</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>0.096781,0.283127,0.151096,0.063365,0.515112,0.065819,0.466132,0.355266,0.036549,0.114545,0.909799,0.637665,0.520335,0.200183,0.200479,0.416542,0.393772,0.281202,0.527772,0.017628,0.542724,0.391743,0.007453,0.322639</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>0.3132386395177948</v>
+      </c>
       <c r="K70" t="inlineStr">
         <is>
           <t>120.501465,120.560944,120.508514,120.276855,120.590485,120.617264,120.351067,120.462769,120.497200,120.463974,120.632217,120.570084,120.482819,120.491013,120.618759,120.599747,120.495895,120.489388,120.492783,120.251740,120.313690,120.375122,120.328949,120.025352</t>
@@ -7348,6 +7404,49 @@
       <c r="M70" t="inlineStr">
         <is>
           <t>120.054169,119.897003,119.768127,119.741356,119.476250,119.445740,119.363235,119.165192,119.202026,119.080673,118.864471,118.936768,118.902451,118.720993,118.610138,118.661133,118.535492,118.376495,118.182724,118.133347,117.963440,117.821472,117.757523,117.737076</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-09-27 05:02:20</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>24</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>120.223595,120.036514,120.023254,119.988464,119.864006,119.852127,119.844704,119.751961,119.699089,119.714035,119.585449,119.548981,119.447632,119.352425,119.300598,119.282913,119.268295,119.203873,119.139526,119.146759,119.124786,119.023071,118.933517,118.842079</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>120.010719,120.062149,119.902863,119.722824,119.967407,119.789963,119.583321,119.537140,119.497704,119.444443,119.446739,119.178711,119.173103,119.082703,119.062759,119.015251,118.849846,118.797318,118.912552,118.662865,118.620438,118.743156,118.594498,118.383804</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>119.294464,119.004700,118.743027,118.601669,118.249924,117.986969,117.973518,117.736855,117.400406,117.208618,116.839447,116.732880,116.517448,116.332428,116.057693,115.946579,115.704834,115.622246,115.216446,115.069565,114.985550,114.834480,114.684410,114.572937</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>119.686340,119.407951,119.281067,119.155846,118.862541,118.744629,118.706268,118.498199,118.359421,118.159821,117.834717,117.794792,117.683655,117.417778,117.257172,117.238525,117.069115,116.913116,116.756218,116.727829,116.605354,116.360672,116.329788,116.186081</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J71"/>
+  <dimension ref="A1:J72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3115,6 +3115,44 @@
       </c>
       <c r="F71" t="n">
         <v>118.8420791625977</v>
+      </c>
+      <c r="G71" t="n">
+        <v>119.7699966430664</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.9279174804687074</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.7747495253206432</v>
+      </c>
+      <c r="J71" t="n">
+        <v>2.184420337333937</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-09-28 05:04:04</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>24</v>
+      </c>
+      <c r="F72" t="n">
+        <v>119.7176666259766</v>
       </c>
     </row>
   </sheetData>
@@ -3128,7 +3166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M71"/>
+  <dimension ref="A1:M72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7434,6 +7472,24 @@
           <t>120.223595,120.036514,120.023254,119.988464,119.864006,119.852127,119.844704,119.751961,119.699089,119.714035,119.585449,119.548981,119.447632,119.352425,119.300598,119.282913,119.268295,119.203873,119.139526,119.146759,119.124786,119.023071,118.933517,118.842079</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>121.309998,123.980003,124.089996,124.440002,124.000000,123.900002,123.320000,123.139999,121.690002,121.750000,121.809998,122.050003,123.279999,123.019997,122.690002,122.830002,121.370003,121.980003,121.660004,120.709999,120.000000,119.820000,119.959999,119.769997</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>1.086403,3.943489,4.066742,4.451538,4.135994,4.047875,3.475296,3.388038,1.990913,2.035965,2.224549,2.501022,3.832367,3.667572,3.389404,3.547089,2.101708,2.776130,2.520478,1.563240,0.875214,0.796929,1.026482,0.927918</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>0.895559,3.180746,3.277252,3.577257,3.335479,3.267050,2.818112,2.751371,1.636053,1.672251,1.826245,2.049178,3.108669,2.981281,2.762576,2.887803,1.731653,2.275890,2.071739,1.295038,0.729345,0.665105,0.855687,0.774750</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>2.184420337333937</v>
+      </c>
       <c r="K71" t="inlineStr">
         <is>
           <t>120.010719,120.062149,119.902863,119.722824,119.967407,119.789963,119.583321,119.537140,119.497704,119.444443,119.446739,119.178711,119.173103,119.082703,119.062759,119.015251,118.849846,118.797318,118.912552,118.662865,118.620438,118.743156,118.594498,118.383804</t>
@@ -7447,6 +7503,49 @@
       <c r="M71" t="inlineStr">
         <is>
           <t>119.686340,119.407951,119.281067,119.155846,118.862541,118.744629,118.706268,118.498199,118.359421,118.159821,117.834717,117.794792,117.683655,117.417778,117.257172,117.238525,117.069115,116.913116,116.756218,116.727829,116.605354,116.360672,116.329788,116.186081</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-09-28 05:04:04</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>24</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>119.846565,119.710709,119.663521,119.620628,119.498100,119.426094,119.445412,119.345619,119.284470,119.301010,119.240356,119.329590,119.331459,119.333740,119.400681,119.490646,119.589539,119.542282,119.600845,119.671097,119.642288,119.715439,119.707420,119.717667</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>119.555542,119.840195,119.585403,119.377899,119.456268,119.475029,119.227463,119.173691,119.059433,119.215363,119.071686,119.087997,119.030319,119.130478,119.162521,119.293076,119.300262,119.146271,119.461792,119.241707,119.292381,119.413597,119.431885,119.366402</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>118.826996,118.424194,118.084366,117.843262,117.486504,117.191498,117.148514,116.863586,116.583633,116.377197,116.024582,116.117409,116.058609,115.948807,115.856567,115.839035,115.832092,115.760704,115.400223,115.259232,115.291031,115.248558,115.219421,115.248337</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>119.259064,118.905739,118.671112,118.533669,118.211037,117.983421,117.928299,117.706421,117.615273,117.375298,117.115517,117.269722,117.270767,117.065674,117.076370,117.167297,117.174179,116.981110,116.948051,116.995895,116.894547,116.843475,116.939880,116.810493</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J72"/>
+  <dimension ref="A1:J73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3153,6 +3153,44 @@
       </c>
       <c r="F72" t="n">
         <v>119.7176666259766</v>
+      </c>
+      <c r="G72" t="n">
+        <v>118.0800018310547</v>
+      </c>
+      <c r="H72" t="n">
+        <v>1.637664794921918</v>
+      </c>
+      <c r="I72" t="n">
+        <v>1.386911220805229</v>
+      </c>
+      <c r="J72" t="n">
+        <v>1.042860221901375</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-09-29 05:28:49</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>24</v>
+      </c>
+      <c r="F73" t="n">
+        <v>118.1971435546875</v>
       </c>
     </row>
   </sheetData>
@@ -3166,7 +3204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M72"/>
+  <dimension ref="A1:M73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7533,6 +7571,24 @@
           <t>119.846565,119.710709,119.663521,119.620628,119.498100,119.426094,119.445412,119.345619,119.284470,119.301010,119.240356,119.329590,119.331459,119.333740,119.400681,119.490646,119.589539,119.542282,119.600845,119.671097,119.642288,119.715439,119.707420,119.717667</t>
         </is>
       </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>118.690002,117.989998,118.300003,117.720001,118.430000,118.690002,119.989998,119.809998,118.000000,118.709999,119.260002,119.699997,119.949997,118.320000,118.779999,117.680000,118.540001,118.820000,118.070000,117.059998,116.900002,117.809998,117.650002,118.080002</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>1.156563,1.720711,1.363518,1.900627,1.068100,0.736092,0.544586,0.464379,1.284470,0.591011,0.019646,0.370407,0.618538,1.013740,0.620682,1.810646,1.049538,0.722282,1.530845,2.611099,2.742286,1.905441,2.057418,1.637665</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>0.974440,1.458353,1.152593,1.614532,0.901883,0.620180,0.453859,0.387596,1.088534,0.497861,0.016473,0.309446,0.515663,0.856778,0.522548,1.538618,0.885387,0.607879,1.296557,2.230565,2.345840,1.617385,1.748762,1.386912</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>1.042860221901375</v>
+      </c>
       <c r="K72" t="inlineStr">
         <is>
           <t>119.555542,119.840195,119.585403,119.377899,119.456268,119.475029,119.227463,119.173691,119.059433,119.215363,119.071686,119.087997,119.030319,119.130478,119.162521,119.293076,119.300262,119.146271,119.461792,119.241707,119.292381,119.413597,119.431885,119.366402</t>
@@ -7546,6 +7602,49 @@
       <c r="M72" t="inlineStr">
         <is>
           <t>119.259064,118.905739,118.671112,118.533669,118.211037,117.983421,117.928299,117.706421,117.615273,117.375298,117.115517,117.269722,117.270767,117.065674,117.076370,117.167297,117.174179,116.981110,116.948051,116.995895,116.894547,116.843475,116.939880,116.810493</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-09-29 05:28:49</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>24</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>118.050171,118.009018,118.003571,118.093491,118.053345,118.101288,118.167572,118.123573,118.143036,118.121216,118.097488,118.158600,118.127548,118.133163,118.080612,118.121140,118.169693,118.106712,118.132851,118.116524,118.145157,118.142242,118.095161,118.197144</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>117.923599,118.228104,117.841949,117.994904,118.076935,118.241852,118.144272,118.101639,118.164154,118.092133,118.015915,117.884079,118.070633,118.241623,118.103821,118.106674,117.884583,118.021324,118.259613,117.754837,117.900757,117.915146,118.037399,117.934921</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>116.878006,116.516602,116.307449,116.371948,115.909203,115.787827,115.806107,115.561813,115.393044,115.156128,114.978546,115.012039,114.868851,114.787086,114.518723,114.485916,114.364502,114.257645,113.781769,113.708138,113.803040,113.669762,113.506348,113.634506</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>117.393890,117.111885,116.931923,116.983627,116.712662,116.664772,116.599503,116.445465,116.442200,116.212051,116.016945,116.126022,116.123123,115.911041,115.746346,115.736511,115.699394,115.450027,115.315460,115.428619,115.393234,115.190704,115.259048,115.293373</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J73"/>
+  <dimension ref="A1:J74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3191,6 +3191,44 @@
       </c>
       <c r="F73" t="n">
         <v>118.1971435546875</v>
+      </c>
+      <c r="G73" t="n">
+        <v>118.4700012207031</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.272857666015625</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.230317939735061</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.9682798619354187</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-09-30 05:16:27</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>24</v>
+      </c>
+      <c r="F74" t="n">
+        <v>117.2572555541992</v>
       </c>
     </row>
   </sheetData>
@@ -3204,7 +3242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M73"/>
+  <dimension ref="A1:M74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7632,6 +7670,24 @@
           <t>118.050171,118.009018,118.003571,118.093491,118.053345,118.101288,118.167572,118.123573,118.143036,118.121216,118.097488,118.158600,118.127548,118.133163,118.080612,118.121140,118.169693,118.106712,118.132851,118.116524,118.145157,118.142242,118.095161,118.197144</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>119.199997,119.489998,119.139999,119.879997,119.389999,120.120003,120.860001,120.949997,120.190002,118.190002,118.019997,117.699997,119.120003,118.779999,119.019997,118.919998,119.089996,119.080002,118.910004,119.410004,119.650002,119.110001,118.739998,118.470001</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>1.149826,1.480980,1.136428,1.786506,1.336654,2.018715,2.692429,2.826424,2.046966,0.068786,0.077491,0.458603,0.992455,0.646836,0.939385,0.798858,0.920303,0.973290,0.777153,1.293480,1.504845,0.967759,0.644837,0.272857</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>0.964619,1.239417,0.953860,1.490245,1.119570,1.680582,2.227725,2.336853,1.703109,0.058200,0.065660,0.389637,0.833155,0.544566,0.789266,0.671761,0.772780,0.817341,0.653564,1.083226,1.257705,0.812491,0.543066,0.230318</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>0.9682798619354187</v>
+      </c>
       <c r="K73" t="inlineStr">
         <is>
           <t>117.923599,118.228104,117.841949,117.994904,118.076935,118.241852,118.144272,118.101639,118.164154,118.092133,118.015915,117.884079,118.070633,118.241623,118.103821,118.106674,117.884583,118.021324,118.259613,117.754837,117.900757,117.915146,118.037399,117.934921</t>
@@ -7645,6 +7701,49 @@
       <c r="M73" t="inlineStr">
         <is>
           <t>117.393890,117.111885,116.931923,116.983627,116.712662,116.664772,116.599503,116.445465,116.442200,116.212051,116.016945,116.126022,116.123123,115.911041,115.746346,115.736511,115.699394,115.450027,115.315460,115.428619,115.393234,115.190704,115.259048,115.293373</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-09-30 05:16:27</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>24</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>118.584648,118.429703,118.312103,118.281708,118.191147,118.087730,118.010872,117.955482,117.835144,117.778656,117.640991,117.657639,117.616562,117.536743,117.541664,117.522232,117.496918,117.442337,117.444153,117.383583,117.374420,117.338982,117.205055,117.257256</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>118.426086,118.556885,118.164162,118.024216,118.195107,117.943680,117.978767,117.960983,117.768333,117.750496,117.561493,117.215988,117.449287,117.384552,117.526680,117.373215,117.245819,117.137436,117.359039,117.094803,117.292831,117.089722,116.941933,117.090805</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>117.085175,116.727188,116.479172,116.456573,116.087891,115.876060,115.787239,115.641266,115.318329,115.109489,114.776260,114.775009,114.671524,114.591614,114.503601,114.360115,114.180092,114.085251,113.681946,113.607681,113.646393,113.562027,113.357758,113.353485</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>117.718636,117.409576,117.195023,117.127937,116.851051,116.720276,116.558716,116.517792,116.402756,116.104858,115.833817,115.800690,115.816406,115.645416,115.582382,115.518906,115.444359,115.163300,115.133896,115.116447,115.007614,114.848083,114.856651,114.798523</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J74"/>
+  <dimension ref="A1:J75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3229,6 +3229,44 @@
       </c>
       <c r="F74" t="n">
         <v>117.2572555541992</v>
+      </c>
+      <c r="G74" t="n">
+        <v>119.1999969482422</v>
+      </c>
+      <c r="H74" t="n">
+        <v>1.942741394042983</v>
+      </c>
+      <c r="I74" t="n">
+        <v>1.629816647467315</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.99637933180201</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-10-01 05:31:34</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>24</v>
+      </c>
+      <c r="F75" t="n">
+        <v>118.5102996826172</v>
       </c>
     </row>
   </sheetData>
@@ -3242,7 +3280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M74"/>
+  <dimension ref="A1:M75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7731,6 +7769,24 @@
           <t>118.584648,118.429703,118.312103,118.281708,118.191147,118.087730,118.010872,117.955482,117.835144,117.778656,117.640991,117.657639,117.616562,117.536743,117.541664,117.522232,117.496918,117.442337,117.444153,117.383583,117.374420,117.338982,117.205055,117.257256</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>118.050003,118.430000,118.169998,119.279999,119.830002,119.459999,121.870003,121.010002,118.779999,119.260002,120.269997,119.150002,118.669998,117.180000,117.980003,118.000000,118.099998,118.059998,117.940002,118.029999,118.120003,118.589996,119.029999,119.199997</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>0.534645,0.000297,0.142105,0.998291,1.638855,1.372269,3.859131,3.054520,0.944855,1.481346,2.629006,1.492363,1.053436,0.356743,0.438339,0.477768,0.603080,0.617661,0.495849,0.646416,0.745583,1.251014,1.824944,1.942741</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>0.452897,0.000251,0.120255,0.836931,1.367650,1.148727,3.166596,2.524188,0.795466,1.242115,2.185920,1.252507,0.887702,0.304440,0.371537,0.404888,0.510652,0.523175,0.420425,0.547671,0.631208,1.054907,1.533180,1.629816</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>0.99637933180201</v>
+      </c>
       <c r="K74" t="inlineStr">
         <is>
           <t>118.426086,118.556885,118.164162,118.024216,118.195107,117.943680,117.978767,117.960983,117.768333,117.750496,117.561493,117.215988,117.449287,117.384552,117.526680,117.373215,117.245819,117.137436,117.359039,117.094803,117.292831,117.089722,116.941933,117.090805</t>
@@ -7744,6 +7800,49 @@
       <c r="M74" t="inlineStr">
         <is>
           <t>117.718636,117.409576,117.195023,117.127937,116.851051,116.720276,116.558716,116.517792,116.402756,116.104858,115.833817,115.800690,115.816406,115.645416,115.582382,115.518906,115.444359,115.163300,115.133896,115.116447,115.007614,114.848083,114.856651,114.798523</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-10-01 05:31:34</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>24</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>119.241936,119.105598,119.039017,119.061783,119.005737,118.966454,119.011215,118.985588,118.940887,118.923309,118.845901,118.870056,118.841064,118.795898,118.785591,118.784973,118.752060,118.746231,118.710434,118.669510,118.705170,118.617401,118.507553,118.510300</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>119.097229,119.285660,118.936081,118.947342,119.147728,118.869049,119.067101,118.921928,118.856522,118.794083,118.757225,118.622665,118.688736,118.733856,118.758453,118.434921,118.635376,118.551620,118.719429,118.443466,118.480377,118.292374,118.325157,118.389656</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>117.987335,117.703400,117.483749,117.491669,117.214371,117.118118,117.118835,116.990768,116.840355,116.721848,116.588364,116.449860,116.315292,116.183640,116.219284,116.069336,115.910294,115.887314,115.502319,115.343185,115.443665,115.278519,115.168289,115.127792</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>118.493584,118.225510,118.070267,118.022766,117.874199,117.745796,117.802139,117.719360,117.720627,117.522354,117.363625,117.359070,117.352905,117.130219,117.176880,117.134140,117.003601,116.908493,116.749847,116.685562,116.648964,116.548668,116.497658,116.406342</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J75"/>
+  <dimension ref="A1:J76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3267,6 +3267,44 @@
       </c>
       <c r="F75" t="n">
         <v>118.5102996826172</v>
+      </c>
+      <c r="G75" t="n">
+        <v>122.9300003051758</v>
+      </c>
+      <c r="H75" t="n">
+        <v>4.41970062255858</v>
+      </c>
+      <c r="I75" t="n">
+        <v>3.595298634659236</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1.135295424676872</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-10-02 05:19:10</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>24</v>
+      </c>
+      <c r="F76" t="n">
+        <v>122.0589370727539</v>
       </c>
     </row>
   </sheetData>
@@ -3280,7 +3318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M75"/>
+  <dimension ref="A1:M76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7830,6 +7868,24 @@
           <t>119.241936,119.105598,119.039017,119.061783,119.005737,118.966454,119.011215,118.985588,118.940887,118.923309,118.845901,118.870056,118.841064,118.795898,118.785591,118.784973,118.752060,118.746231,118.710434,118.669510,118.705170,118.617401,118.507553,118.510300</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>119.169998,117.430000,117.849998,117.650002,117.959999,117.919998,117.309998,117.970001,117.349998,117.320000,117.080002,118.330002,118.349998,118.190002,118.110001,117.629997,118.279999,118.379997,118.839996,119.480003,120.019997,121.190002,123.430000,122.930000</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>0.071938,1.675598,1.189019,1.411781,1.045738,1.046456,1.701217,1.015587,1.590889,1.603309,1.765899,0.540054,0.491066,0.605896,0.675590,1.154976,0.472061,0.366234,0.129562,0.810493,1.314827,2.572601,4.922447,4.419700</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>0.060366,1.426891,1.008925,1.199984,0.886519,0.887429,1.450190,0.860886,1.355678,1.366612,1.508284,0.456397,0.414927,0.512645,0.572001,0.981872,0.399105,0.309371,0.109023,0.678351,1.095506,2.122784,3.988048,3.595298</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>1.135295424676872</v>
+      </c>
       <c r="K75" t="inlineStr">
         <is>
           <t>119.097229,119.285660,118.936081,118.947342,119.147728,118.869049,119.067101,118.921928,118.856522,118.794083,118.757225,118.622665,118.688736,118.733856,118.758453,118.434921,118.635376,118.551620,118.719429,118.443466,118.480377,118.292374,118.325157,118.389656</t>
@@ -7843,6 +7899,49 @@
       <c r="M75" t="inlineStr">
         <is>
           <t>118.493584,118.225510,118.070267,118.022766,117.874199,117.745796,117.802139,117.719360,117.720627,117.522354,117.363625,117.359070,117.352905,117.130219,117.176880,117.134140,117.003601,116.908493,116.749847,116.685562,116.648964,116.548668,116.497658,116.406342</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-10-02 05:19:10</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>24</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>122.640251,122.621857,122.650581,122.665413,122.603622,122.560471,122.643677,122.668968,122.687881,122.577530,122.614738,122.544350,122.489891,122.375137,122.375053,122.314957,122.362381,122.272705,122.204254,122.151978,122.126625,122.139969,122.095139,122.058937</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>122.444954,122.561295,122.677185,122.565262,122.575531,122.582047,122.531136,122.736298,122.451462,122.670044,122.525902,122.320290,122.295898,122.232956,122.166176,122.095627,122.028793,122.018951,122.046478,121.849167,121.863464,121.957870,122.011551,121.891129</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>121.175133,120.874496,120.633018,120.512169,120.202164,120.022530,119.900742,119.754547,119.672401,119.369530,119.320282,119.114273,119.050888,118.723709,118.585648,118.482117,118.420029,118.391167,117.943008,117.729607,117.730194,117.636818,117.472229,117.493942</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>121.764801,121.493851,121.379578,121.287704,121.067192,120.808670,120.808182,120.685242,120.757446,120.444382,120.330093,120.273560,120.218681,119.886688,119.833679,119.868973,119.802338,119.603226,119.369171,119.299820,119.147133,119.140015,119.069290,118.963806</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J76"/>
+  <dimension ref="A1:J77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3305,6 +3305,44 @@
       </c>
       <c r="F76" t="n">
         <v>122.0589370727539</v>
+      </c>
+      <c r="G76" t="n">
+        <v>119.0800018310547</v>
+      </c>
+      <c r="H76" t="n">
+        <v>2.978935241699219</v>
+      </c>
+      <c r="I76" t="n">
+        <v>2.501625122516875</v>
+      </c>
+      <c r="J76" t="n">
+        <v>2.066313207961998</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-10-03 05:02:00</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>24</v>
+      </c>
+      <c r="F77" t="n">
+        <v>118.7760620117188</v>
       </c>
     </row>
   </sheetData>
@@ -3318,7 +3356,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M76"/>
+  <dimension ref="A1:M77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7929,6 +7967,24 @@
           <t>122.640251,122.621857,122.650581,122.665413,122.603622,122.560471,122.643677,122.668968,122.687881,122.577530,122.614738,122.544350,122.489891,122.375137,122.375053,122.314957,122.362381,122.272705,122.204254,122.151978,122.126625,122.139969,122.095139,122.058937</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>121.720001,121.680000,122.029999,121.760002,121.889999,121.800003,122.540001,122.050003,120.610001,119.949997,119.959999,119.690002,118.120003,117.949997,117.769997,118.190002,118.510002,118.580002,118.959999,119.110001,118.889999,119.389999,119.150002,119.080002</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>0.920250,0.941857,0.620582,0.905411,0.713623,0.760468,0.103676,0.618965,2.077880,2.627533,2.654739,2.854348,4.369888,4.425140,4.605056,4.124955,3.852379,3.692703,3.244255,3.041977,3.236626,2.749970,2.945137,2.978935</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>0.756038,0.774044,0.508549,0.743603,0.585464,0.624358,0.084606,0.507140,1.722809,2.190524,2.213020,2.384784,3.699533,3.751708,3.910212,3.490104,3.250678,3.114103,2.727181,2.553923,2.722370,2.303350,2.471790,2.501625</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>2.066313207961998</v>
+      </c>
       <c r="K76" t="inlineStr">
         <is>
           <t>122.444954,122.561295,122.677185,122.565262,122.575531,122.582047,122.531136,122.736298,122.451462,122.670044,122.525902,122.320290,122.295898,122.232956,122.166176,122.095627,122.028793,122.018951,122.046478,121.849167,121.863464,121.957870,122.011551,121.891129</t>
@@ -7942,6 +7998,49 @@
       <c r="M76" t="inlineStr">
         <is>
           <t>121.764801,121.493851,121.379578,121.287704,121.067192,120.808670,120.808182,120.685242,120.757446,120.444382,120.330093,120.273560,120.218681,119.886688,119.833679,119.868973,119.802338,119.603226,119.369171,119.299820,119.147133,119.140015,119.069290,118.963806</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-10-03 05:02:00</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>24</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>119.130539,119.113968,119.049286,119.079803,118.958557,118.884644,118.866104,118.817947,118.779236,118.679893,118.672638,118.650993,118.613052,118.588249,118.622116,118.600616,118.676117,118.670486,118.712914,118.695442,118.722870,118.732468,118.731506,118.776062</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>118.973427,119.113312,119.021362,118.942978,118.960815,118.932617,118.864456,118.842285,118.675491,118.621109,118.605408,118.423325,118.429718,118.523254,118.477798,118.489838,118.382614,118.503159,118.545456,118.453506,118.628693,118.583954,118.748970,118.642647</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>117.972588,117.745735,117.503632,117.499695,117.104706,116.965591,116.803482,116.606720,116.441254,116.211884,116.076843,115.967636,115.902908,115.801224,115.698578,115.601562,115.529076,115.566750,115.296921,115.194778,115.302597,115.243515,115.224449,115.257309</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>118.459236,118.257736,118.100357,118.033127,117.795166,117.574440,117.491302,117.345268,117.363724,117.096298,116.920044,116.889618,116.904480,116.733139,116.727234,116.745537,116.717796,116.583939,116.571030,116.542252,116.532341,116.477348,116.530914,116.504944</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J77"/>
+  <dimension ref="A1:J78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3343,6 +3343,44 @@
       </c>
       <c r="F77" t="n">
         <v>118.7760620117188</v>
+      </c>
+      <c r="G77" t="n">
+        <v>120.7600021362305</v>
+      </c>
+      <c r="H77" t="n">
+        <v>1.983940124511662</v>
+      </c>
+      <c r="I77" t="n">
+        <v>1.642878510612778</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.8512986838207035</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-10-04 05:34:22</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>24</v>
+      </c>
+      <c r="F78" t="n">
+        <v>120.8331909179688</v>
       </c>
     </row>
   </sheetData>
@@ -3356,7 +3394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M77"/>
+  <dimension ref="A1:M78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8028,6 +8066,24 @@
           <t>119.130539,119.113968,119.049286,119.079803,118.958557,118.884644,118.866104,118.817947,118.779236,118.679893,118.672638,118.650993,118.613052,118.588249,118.622116,118.600616,118.676117,118.670486,118.712914,118.695442,118.722870,118.732468,118.731506,118.776062</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>119.430000,119.320000,119.269997,119.309998,119.480003,119.300003,119.459999,119.410004,119.760002,119.680000,119.699997,119.980003,119.919998,119.779999,119.790001,119.629997,119.699997,119.589996,120.169998,120.129997,120.400002,120.760002,120.620003,120.760002</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>0.299461,0.206032,0.220711,0.230195,0.521446,0.415359,0.593895,0.592057,0.980766,1.000107,1.027359,1.329010,1.306946,1.191750,1.167885,1.029381,1.023880,0.919510,1.457084,1.434555,1.677132,2.027534,1.888497,1.983940</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>0.250742,0.172672,0.185051,0.192938,0.436430,0.348163,0.497150,0.495818,0.818943,0.835651,0.858278,1.107693,1.089848,0.994949,0.974944,0.860471,0.855372,0.768886,1.212519,1.194169,1.392966,1.678978,1.565658,1.642879</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>0.8512986838207035</v>
+      </c>
       <c r="K77" t="inlineStr">
         <is>
           <t>118.973427,119.113312,119.021362,118.942978,118.960815,118.932617,118.864456,118.842285,118.675491,118.621109,118.605408,118.423325,118.429718,118.523254,118.477798,118.489838,118.382614,118.503159,118.545456,118.453506,118.628693,118.583954,118.748970,118.642647</t>
@@ -8041,6 +8097,49 @@
       <c r="M77" t="inlineStr">
         <is>
           <t>118.459236,118.257736,118.100357,118.033127,117.795166,117.574440,117.491302,117.345268,117.363724,117.096298,116.920044,116.889618,116.904480,116.733139,116.727234,116.745537,116.717796,116.583939,116.571030,116.542252,116.532341,116.477348,116.530914,116.504944</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-10-04 05:34:22</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>24</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>120.751793,120.818237,120.801483,120.948196,120.851074,120.886169,120.951004,120.849121,120.870422,120.868919,120.854912,120.871704,120.760864,120.728302,120.721642,120.787323,120.823044,120.775597,120.809921,120.776237,120.799072,120.777512,120.804947,120.833191</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>120.649902,120.748306,120.827843,120.826553,120.892365,120.768501,120.984711,120.892090,120.715012,120.815414,120.773621,120.563553,120.607086,120.596092,120.492081,120.680450,120.535950,120.629990,120.658691,120.551178,120.665428,120.641068,120.697876,120.658997</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>119.961380,119.974258,119.844070,119.977737,119.643951,119.580536,119.530136,119.237686,119.170685,119.023155,118.876816,118.793625,118.593552,118.561432,118.400436,118.406487,118.353180,118.317810,118.001938,117.887115,117.968559,117.836929,117.808395,117.856125</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>120.328896,120.320862,120.263214,120.349426,120.144730,120.035065,120.026421,119.865082,119.929810,119.712837,119.548111,119.555153,119.503067,119.336700,119.261398,119.362328,119.400780,119.198059,119.155853,119.125092,119.055878,118.936539,118.945526,118.902359</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J78"/>
+  <dimension ref="A1:J79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3381,6 +3381,44 @@
       </c>
       <c r="F78" t="n">
         <v>120.8331909179688</v>
+      </c>
+      <c r="G78" t="n">
+        <v>120.3000030517578</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.5331878662109943</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.4432151726393522</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.4151658921671975</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-10-05 05:18:05</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>24</v>
+      </c>
+      <c r="F79" t="n">
+        <v>120.1840057373047</v>
       </c>
     </row>
   </sheetData>
@@ -3394,7 +3432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M78"/>
+  <dimension ref="A1:M79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8127,6 +8165,24 @@
           <t>120.751793,120.818237,120.801483,120.948196,120.851074,120.886169,120.951004,120.849121,120.870422,120.868919,120.854912,120.871704,120.760864,120.728302,120.721642,120.787323,120.823044,120.775597,120.809921,120.776237,120.799072,120.777512,120.804947,120.833191</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>120.940002,121.110001,120.940002,121.290001,121.260002,121.220001,121.279999,121.699997,121.839996,121.540001,121.720001,121.470001,121.459999,121.080002,121.239998,121.169998,121.709999,121.570000,121.300003,121.139999,121.169998,120.400002,120.470001,120.300003</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>0.188209,0.291764,0.138519,0.341805,0.408928,0.333832,0.328995,0.850876,0.969574,0.671082,0.865089,0.598297,0.699135,0.351700,0.518356,0.382675,0.886955,0.794403,0.490082,0.363762,0.370926,0.377510,0.334946,0.533188</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>0.155622,0.240908,0.114536,0.281808,0.337232,0.275394,0.271269,0.699159,0.795777,0.552149,0.710721,0.492547,0.575609,0.290469,0.427545,0.315817,0.728745,0.653453,0.404025,0.300283,0.306120,0.313547,0.278033,0.443215</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>0.4151658921671975</v>
+      </c>
       <c r="K78" t="inlineStr">
         <is>
           <t>120.649902,120.748306,120.827843,120.826553,120.892365,120.768501,120.984711,120.892090,120.715012,120.815414,120.773621,120.563553,120.607086,120.596092,120.492081,120.680450,120.535950,120.629990,120.658691,120.551178,120.665428,120.641068,120.697876,120.658997</t>
@@ -8140,6 +8196,49 @@
       <c r="M78" t="inlineStr">
         <is>
           <t>120.328896,120.320862,120.263214,120.349426,120.144730,120.035065,120.026421,119.865082,119.929810,119.712837,119.548111,119.555153,119.503067,119.336700,119.261398,119.362328,119.400780,119.198059,119.155853,119.125092,119.055878,118.936539,118.945526,118.902359</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-10-05 05:18:05</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>24</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>120.266937,120.214729,120.090698,120.173706,120.068947,120.117569,120.138214,120.075340,120.114960,120.153915,120.075661,120.170387,120.052444,120.033005,120.062790,120.119308,120.155846,120.102173,120.130127,120.173828,120.221375,120.180801,120.171448,120.184006</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>120.199829,120.246902,120.049103,120.100098,120.179291,120.101120,120.155487,120.104080,120.023849,120.124298,120.036240,119.907669,119.911575,119.974182,119.826889,119.916153,119.757072,119.796349,120.022339,119.818039,120.028015,120.013077,119.961548,119.946182</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>119.656990,119.592148,119.272339,119.259651,118.967125,118.907677,118.766571,118.550156,118.466896,118.336014,118.156906,118.137253,117.896324,117.945961,117.782639,117.739426,117.675369,117.575455,117.287270,117.212357,117.274033,117.148407,117.128174,117.150887</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>119.956779,119.849792,119.594345,119.598701,119.365829,119.312111,119.276230,119.156166,119.178444,119.028473,118.801559,118.911499,118.750107,118.673828,118.670059,118.725250,118.685516,118.551315,118.506729,118.466492,118.453247,118.352997,118.331787,118.315269</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J79"/>
+  <dimension ref="A1:J80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3419,6 +3419,44 @@
       </c>
       <c r="F79" t="n">
         <v>120.1840057373047</v>
+      </c>
+      <c r="G79" t="n">
+        <v>119.7799987792969</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.4040069580078267</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.3372908349683975</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.4676205124475311</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-10-06 06:02:14</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>24</v>
+      </c>
+      <c r="F80" t="n">
+        <v>119.7821655273438</v>
       </c>
     </row>
   </sheetData>
@@ -3432,7 +3470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M79"/>
+  <dimension ref="A1:M80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8226,6 +8264,24 @@
           <t>120.266937,120.214729,120.090698,120.173706,120.068947,120.117569,120.138214,120.075340,120.114960,120.153915,120.075661,120.170387,120.052444,120.033005,120.062790,120.119308,120.155846,120.102173,120.130127,120.173828,120.221375,120.180801,120.171448,120.184006</t>
         </is>
       </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>121.550003,121.660004,121.029999,120.610001,120.650002,120.809998,120.339996,120.790001,119.489998,119.320000,119.599998,120.010002,120.089996,120.269997,120.639999,120.800003,121.040001,120.769997,121.019997,120.620003,120.190002,119.980003,120.070000,119.779999</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>1.283066,1.445275,0.939301,0.436295,0.581055,0.692429,0.201782,0.714661,0.624962,0.833915,0.475663,0.160385,0.037552,0.236992,0.577209,0.680695,0.884155,0.667824,0.889870,0.446175,0.031373,0.200798,0.101448,0.404007</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1.055587,1.187962,0.776089,0.361740,0.481603,0.573155,0.167677,0.591656,0.523025,0.698890,0.397711,0.133643,0.031270,0.197050,0.478456,0.563489,0.730465,0.552971,0.735308,0.369901,0.026102,0.167359,0.084491,0.337291</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>0.4676205124475311</v>
+      </c>
       <c r="K79" t="inlineStr">
         <is>
           <t>120.199829,120.246902,120.049103,120.100098,120.179291,120.101120,120.155487,120.104080,120.023849,120.124298,120.036240,119.907669,119.911575,119.974182,119.826889,119.916153,119.757072,119.796349,120.022339,119.818039,120.028015,120.013077,119.961548,119.946182</t>
@@ -8239,6 +8295,49 @@
       <c r="M79" t="inlineStr">
         <is>
           <t>119.956779,119.849792,119.594345,119.598701,119.365829,119.312111,119.276230,119.156166,119.178444,119.028473,118.801559,118.911499,118.750107,118.673828,118.670059,118.725250,118.685516,118.551315,118.506729,118.466492,118.453247,118.352997,118.331787,118.315269</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-10-06 06:02:14</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>24</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>119.459221,119.484024,119.446671,119.523567,119.495285,119.536560,119.570717,119.546692,119.566727,119.652115,119.599991,119.665405,119.660355,119.661957,119.667130,119.729813,119.768463,119.740517,119.759979,119.802429,119.797729,119.815872,119.768402,119.782166</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>119.440628,119.612305,119.385689,119.529953,119.504211,119.630409,119.565445,119.534180,119.537735,119.631660,119.655418,119.595558,119.530029,119.641479,119.568176,119.553909,119.572472,119.587112,119.745544,119.528458,119.638336,119.593529,119.647186,119.629517</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>118.804077,118.735703,118.505051,118.516197,118.327858,118.258911,118.213013,118.038651,117.910645,117.902809,117.737625,117.712883,117.534134,117.562904,117.478470,117.442596,117.438599,117.415466,117.103722,117.107964,117.081696,117.078735,116.926865,116.923248</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>119.125282,119.029724,118.843460,118.870453,118.754562,118.698044,118.673981,118.632507,118.619835,118.584717,118.360207,118.457047,118.393295,118.349930,118.360832,118.391670,118.369644,118.307037,118.240982,118.276726,118.244804,118.170677,118.073090,118.055565</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J80"/>
+  <dimension ref="A1:J81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3457,6 +3457,44 @@
       </c>
       <c r="F80" t="n">
         <v>119.7821655273438</v>
+      </c>
+      <c r="G80" t="n">
+        <v>118.5699996948242</v>
+      </c>
+      <c r="H80" t="n">
+        <v>1.212165832519588</v>
+      </c>
+      <c r="I80" t="n">
+        <v>1.022320853200189</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.916722272264644</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-10-07 05:37:24</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>24</v>
+      </c>
+      <c r="F81" t="n">
+        <v>118.7420654296875</v>
       </c>
     </row>
   </sheetData>
@@ -3470,7 +3508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M80"/>
+  <dimension ref="A1:M81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8325,6 +8363,24 @@
           <t>119.459221,119.484024,119.446671,119.523567,119.495285,119.536560,119.570717,119.546692,119.566727,119.652115,119.599991,119.665405,119.660355,119.661957,119.667130,119.729813,119.768463,119.740517,119.759979,119.802429,119.797729,119.815872,119.768402,119.782166</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>120.209999,120.459999,119.519997,120.209999,120.320000,120.430000,120.879997,121.760002,120.489998,120.269997,120.849998,120.839996,120.790001,120.989998,121.010002,120.820000,120.690002,120.570000,118.970001,118.269997,118.220001,118.050003,118.570000,118.570000</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>0.750778,0.975975,0.073326,0.686432,0.824715,0.893440,1.309280,2.213310,0.923271,0.617882,1.250007,1.174591,1.129646,1.328041,1.342872,1.090187,0.921539,0.829483,0.789978,1.532432,1.577728,1.765869,1.198402,1.212166</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>0.624555,0.810207,0.061350,0.571027,0.685434,0.741875,1.083124,1.817765,0.766263,0.513745,1.034346,0.972022,0.935215,1.097645,1.109720,0.902323,0.763559,0.687968,0.664014,1.295707,1.334569,1.495865,1.010713,1.022321</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>0.916722272264644</v>
+      </c>
       <c r="K80" t="inlineStr">
         <is>
           <t>119.440628,119.612305,119.385689,119.529953,119.504211,119.630409,119.565445,119.534180,119.537735,119.631660,119.655418,119.595558,119.530029,119.641479,119.568176,119.553909,119.572472,119.587112,119.745544,119.528458,119.638336,119.593529,119.647186,119.629517</t>
@@ -8338,6 +8394,49 @@
       <c r="M80" t="inlineStr">
         <is>
           <t>119.125282,119.029724,118.843460,118.870453,118.754562,118.698044,118.673981,118.632507,118.619835,118.584717,118.360207,118.457047,118.393295,118.349930,118.360832,118.391670,118.369644,118.307037,118.240982,118.276726,118.244804,118.170677,118.073090,118.055565</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-10-07 05:37:24</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>24</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>118.600800,118.580307,118.557991,118.669449,118.632202,118.641823,118.683960,118.649422,118.663971,118.683319,118.673813,118.703667,118.694489,118.673462,118.710190,118.737717,118.765823,118.751678,118.749619,118.780212,118.779694,118.736374,118.766479,118.742065</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>118.543846,118.747368,118.626701,118.708977,118.673569,118.719490,118.785698,118.660858,118.665131,118.625839,118.711502,118.671280,118.614532,118.809341,118.679489,118.565613,118.602234,118.694748,118.764145,118.539803,118.644051,118.454269,118.647400,118.732117</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>117.490959,117.349152,117.165405,117.211426,117.039215,116.960571,116.929710,116.753616,116.681656,116.557205,116.511597,116.498001,116.353226,116.323120,116.305252,116.167809,116.133789,116.090576,115.757507,115.815582,115.791183,115.683624,115.626106,115.530121</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>117.963089,117.794647,117.622292,117.701813,117.582176,117.533974,117.516441,117.461418,117.479546,117.344208,117.214035,117.314590,117.262878,117.161057,117.264236,117.223671,117.168633,117.062973,117.026825,117.059219,117.016212,116.894516,116.886261,116.787872</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J81"/>
+  <dimension ref="A1:J82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3495,6 +3495,44 @@
       </c>
       <c r="F81" t="n">
         <v>118.7420654296875</v>
+      </c>
+      <c r="G81" t="n">
+        <v>115.3199996948242</v>
+      </c>
+      <c r="H81" t="n">
+        <v>3.422065734863281</v>
+      </c>
+      <c r="I81" t="n">
+        <v>2.967452084564019</v>
+      </c>
+      <c r="J81" t="n">
+        <v>1.871879388323834</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-10-08 05:45:42</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>24</v>
+      </c>
+      <c r="F82" t="n">
+        <v>115.7657318115234</v>
       </c>
     </row>
   </sheetData>
@@ -3508,7 +3546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M81"/>
+  <dimension ref="A1:M82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8424,6 +8462,24 @@
           <t>118.600800,118.580307,118.557991,118.669449,118.632202,118.641823,118.683960,118.649422,118.663971,118.683319,118.673813,118.703667,118.694489,118.673462,118.710190,118.737717,118.765823,118.751678,118.749619,118.780212,118.779694,118.736374,118.766479,118.742065</t>
         </is>
       </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>118.779999,118.580002,118.190002,117.739998,117.620003,117.320000,116.360001,116.169998,115.830002,116.720001,116.750000,116.300003,116.070000,115.820000,116.150002,115.540001,115.949997,116.250000,116.360001,116.019997,116.419998,115.660004,114.919998,115.320000</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>0.179199,0.000305,0.367989,0.929451,1.012199,1.321823,2.323959,2.479424,2.833969,1.963318,1.923813,2.403664,2.624489,2.853462,2.560188,3.197716,2.815826,2.501678,2.389618,2.760215,2.359696,3.076370,3.846481,3.422065</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>0.150866,0.000257,0.311353,0.789410,0.860567,1.126682,1.997215,2.134307,2.446662,1.682075,1.647806,2.066779,2.261126,2.463704,2.204209,2.767627,2.428483,2.151981,2.053642,2.379086,2.026882,2.659839,3.347094,2.967452</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>1.871879388323834</v>
+      </c>
       <c r="K81" t="inlineStr">
         <is>
           <t>118.543846,118.747368,118.626701,118.708977,118.673569,118.719490,118.785698,118.660858,118.665131,118.625839,118.711502,118.671280,118.614532,118.809341,118.679489,118.565613,118.602234,118.694748,118.764145,118.539803,118.644051,118.454269,118.647400,118.732117</t>
@@ -8437,6 +8493,49 @@
       <c r="M81" t="inlineStr">
         <is>
           <t>117.963089,117.794647,117.622292,117.701813,117.582176,117.533974,117.516441,117.461418,117.479546,117.344208,117.214035,117.314590,117.262878,117.161057,117.264236,117.223671,117.168633,117.062973,117.026825,117.059219,117.016212,116.894516,116.886261,116.787872</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-10-08 05:45:42</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>24</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>115.284836,115.242264,115.205338,115.269653,115.247818,115.262283,115.365211,115.361984,115.322327,115.371666,115.377823,115.517242,115.514603,115.581985,115.659943,115.686859,115.701569,115.706490,115.785812,115.816628,115.772812,115.733521,115.730881,115.765732</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>115.290985,115.359558,115.265167,115.283669,115.485046,115.395828,115.535088,115.275200,115.410797,115.540840,115.516060,115.730515,115.712341,115.821533,115.789368,115.527267,115.773102,115.906853,115.978737,115.706612,115.818924,115.603149,115.717552,116.127304</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>114.362366,114.213776,113.858658,113.743607,113.583694,113.452194,113.419342,113.292137,113.062325,112.910385,112.791245,112.864426,112.722191,112.630501,112.722488,112.517502,112.500015,112.329689,112.110596,112.162231,112.057632,111.964088,111.900505,111.859421</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>114.755760,114.542351,114.334351,114.255608,114.131439,114.074387,114.059334,113.986069,114.005852,113.814583,113.654709,113.818222,113.761124,113.734291,113.911942,113.770065,113.700439,113.475525,113.586960,113.682663,113.563042,113.359116,113.405373,113.376617</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J82"/>
+  <dimension ref="A1:J83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3533,6 +3533,44 @@
       </c>
       <c r="F82" t="n">
         <v>115.7657318115234</v>
+      </c>
+      <c r="G82" t="n">
+        <v>110.2600021362305</v>
+      </c>
+      <c r="H82" t="n">
+        <v>5.505729675292926</v>
+      </c>
+      <c r="I82" t="n">
+        <v>4.993406102505228</v>
+      </c>
+      <c r="J82" t="n">
+        <v>4.142134169622839</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-10-09 05:49:44</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>24</v>
+      </c>
+      <c r="F83" t="n">
+        <v>111.9216766357422</v>
       </c>
     </row>
   </sheetData>
@@ -3546,7 +3584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M82"/>
+  <dimension ref="A1:M83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8523,6 +8561,24 @@
           <t>115.284836,115.242264,115.205338,115.269653,115.247818,115.262283,115.365211,115.361984,115.322327,115.371666,115.377823,115.517242,115.514603,115.581985,115.659943,115.686859,115.701569,115.706490,115.785812,115.816628,115.772812,115.733521,115.730881,115.765732</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>115.279999,114.870003,114.809998,115.099998,114.339996,113.070000,112.419998,112.180000,112.430000,108.470001,107.629997,106.300003,108.019997,109.080002,109.830002,110.550003,110.279999,109.540001,109.250000,109.349998,110.230003,110.330002,109.820000,110.260002</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>0.004837,0.372261,0.395340,0.169655,0.907822,2.192283,2.945213,3.181984,2.892327,6.901665,7.747826,9.217239,7.494606,6.501983,5.829941,5.136856,5.421570,6.166489,6.535812,6.466630,5.542809,5.403519,5.910881,5.505730</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>0.004196,0.324072,0.344343,0.147398,0.793967,1.938873,2.619830,2.836498,2.572558,6.362741,7.198575,8.670968,6.938166,5.960747,5.308150,4.646636,4.916186,5.629440,5.982437,5.913699,5.028403,4.897597,5.382336,4.993406</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>4.142134169622839</v>
+      </c>
       <c r="K82" t="inlineStr">
         <is>
           <t>115.290985,115.359558,115.265167,115.283669,115.485046,115.395828,115.535088,115.275200,115.410797,115.540840,115.516060,115.730515,115.712341,115.821533,115.789368,115.527267,115.773102,115.906853,115.978737,115.706612,115.818924,115.603149,115.717552,116.127304</t>
@@ -8536,6 +8592,49 @@
       <c r="M82" t="inlineStr">
         <is>
           <t>114.755760,114.542351,114.334351,114.255608,114.131439,114.074387,114.059334,113.986069,114.005852,113.814583,113.654709,113.818222,113.761124,113.734291,113.911942,113.770065,113.700439,113.475525,113.586960,113.682663,113.563042,113.359116,113.405373,113.376617</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-10-09 05:49:44</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>24</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>110.298004,110.309631,110.385475,110.347900,110.331680,110.383072,110.509705,110.432877,110.475052,110.605713,110.562881,110.701248,110.868782,110.969849,111.121002,111.080803,111.276360,111.389908,111.544121,111.571045,111.646538,111.702385,111.780121,111.921677</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>110.468658,110.426575,110.362442,110.496643,110.480301,110.496300,110.858978,110.294205,110.775726,110.907562,110.878555,110.798157,111.182800,111.248550,111.247910,111.063675,111.414993,111.531921,111.727844,111.379807,111.688065,111.597183,112.093262,112.105270</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>108.995895,108.657402,108.386711,108.140114,107.796074,107.733795,107.619873,107.346748,107.160484,107.148361,106.782486,106.786171,106.815536,106.733940,106.863991,106.683151,106.853676,106.654709,106.454216,106.518051,106.462990,106.490036,106.437668,106.511070</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>109.542038,109.250542,109.174843,108.945084,108.705688,108.669510,108.608734,108.386086,108.470520,108.340027,108.053284,108.129135,108.221252,108.239395,108.451859,108.310120,108.523674,108.237816,108.484642,108.550903,108.508736,108.364143,108.532364,108.595718</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J83"/>
+  <dimension ref="A1:J84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3571,6 +3571,44 @@
       </c>
       <c r="F83" t="n">
         <v>111.9216766357422</v>
+      </c>
+      <c r="G83" t="n">
+        <v>110.0400009155273</v>
+      </c>
+      <c r="H83" t="n">
+        <v>1.881675720214858</v>
+      </c>
+      <c r="I83" t="n">
+        <v>1.70999246143167</v>
+      </c>
+      <c r="J83" t="n">
+        <v>1.190611592955239</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-10-10 05:33:06</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>24</v>
+      </c>
+      <c r="F84" t="n">
+        <v>109.8383331298828</v>
       </c>
     </row>
   </sheetData>
@@ -3584,7 +3622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M83"/>
+  <dimension ref="A1:M84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8622,6 +8660,24 @@
           <t>110.298004,110.309631,110.385475,110.347900,110.331680,110.383072,110.509705,110.432877,110.475052,110.605713,110.562881,110.701248,110.868782,110.969849,111.121002,111.080803,111.276360,111.389908,111.544121,111.571045,111.646538,111.702385,111.780121,111.921677</t>
         </is>
       </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>110.550003,110.599998,110.540001,110.300003,109.680000,111.220001,110.339996,109.500000,109.989998,109.639999,109.680000,109.790001,109.379997,108.379997,108.940002,108.940002,109.110001,109.040001,109.290001,109.860001,109.830002,109.599998,109.769997,110.040001</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>0.251999,0.290367,0.154526,0.047897,0.651680,0.836929,0.169709,0.932877,0.485054,0.965714,0.882881,0.911247,1.488785,2.589852,2.181000,2.140801,2.166359,2.349907,2.254120,1.711044,1.816536,2.102387,2.010124,1.881676</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>0.227950,0.262538,0.139792,0.043424,0.594165,0.752499,0.153805,0.851942,0.440998,0.880804,0.804961,0.829991,1.361112,2.389603,2.002019,1.965119,1.985482,2.155087,2.062513,1.557477,1.653953,1.918236,1.831215,1.709993</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>1.190611592955239</v>
+      </c>
       <c r="K83" t="inlineStr">
         <is>
           <t>110.468658,110.426575,110.362442,110.496643,110.480301,110.496300,110.858978,110.294205,110.775726,110.907562,110.878555,110.798157,111.182800,111.248550,111.247910,111.063675,111.414993,111.531921,111.727844,111.379807,111.688065,111.597183,112.093262,112.105270</t>
@@ -8635,6 +8691,49 @@
       <c r="M83" t="inlineStr">
         <is>
           <t>109.542038,109.250542,109.174843,108.945084,108.705688,108.669510,108.608734,108.386086,108.470520,108.340027,108.053284,108.129135,108.221252,108.239395,108.451859,108.310120,108.523674,108.237816,108.484642,108.550903,108.508736,108.364143,108.532364,108.595718</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-10-10 05:33:06</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>24</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>110.073929,110.032166,110.064514,110.014633,110.025513,109.935959,109.896286,109.824783,109.803192,109.751373,109.695793,109.709976,109.719650,109.731514,109.770355,109.727295,109.734451,109.793190,109.755371,109.790375,109.789658,109.798286,109.740616,109.838333</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>110.060226,110.099640,109.920517,109.975746,109.932312,109.961761,109.945755,109.667114,109.821564,109.920967,109.687134,109.762306,109.890709,109.874390,109.943481,109.758194,109.868591,109.997086,110.069763,109.794250,109.896423,109.710892,109.878044,109.976036</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>108.852997,108.545204,108.344810,108.138794,108.041832,107.844742,107.756149,107.527084,107.332199,107.127472,106.974548,106.823845,106.668762,106.498238,106.560753,106.220161,106.296524,106.103210,105.750107,105.717628,105.551010,105.553635,105.467560,105.363945</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>109.390076,109.088303,108.953217,108.794685,108.711884,108.593010,108.450233,108.306541,108.315765,108.098862,107.877869,107.841431,107.761635,107.686264,107.802536,107.577530,107.606018,107.372658,107.365128,107.352608,107.220428,107.103745,107.161705,107.125961</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J84"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3609,6 +3609,44 @@
       </c>
       <c r="F84" t="n">
         <v>109.8383331298828</v>
+      </c>
+      <c r="G84" t="n">
+        <v>109.6100006103516</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0.2283325195312358</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0.2083135829393218</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0.29338895561193</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-10-11 05:28:17</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>24</v>
+      </c>
+      <c r="F85" t="n">
+        <v>109.4708251953125</v>
       </c>
     </row>
   </sheetData>
@@ -3622,7 +3660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M84"/>
+  <dimension ref="A1:M85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8721,6 +8759,24 @@
           <t>110.073929,110.032166,110.064514,110.014633,110.025513,109.935959,109.896286,109.824783,109.803192,109.751373,109.695793,109.709976,109.719650,109.731514,109.770355,109.727295,109.734451,109.793190,109.755371,109.790375,109.789658,109.798286,109.740616,109.838333</t>
         </is>
       </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>109.730003,109.849998,109.910004,109.839996,109.589996,109.769997,109.650002,109.830002,110.400002,110.370003,109.949997,109.860001,110.190002,110.339996,110.250000,110.209999,110.379997,109.980003,109.800003,109.940002,109.910004,109.050003,109.489998,109.610001</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>0.343926,0.182168,0.154510,0.174637,0.435517,0.165962,0.246284,0.005219,0.596810,0.618630,0.254204,0.150025,0.470352,0.608482,0.479645,0.482704,0.645546,0.186813,0.044632,0.149627,0.120346,0.748283,0.250618,0.228332</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>0.313429,0.165833,0.140579,0.158992,0.397405,0.151191,0.224610,0.004752,0.540588,0.560505,0.231200,0.136560,0.426856,0.551461,0.435052,0.437986,0.584840,0.169861,0.040648,0.136099,0.109495,0.686183,0.228896,0.208313</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>0.29338895561193</v>
+      </c>
       <c r="K84" t="inlineStr">
         <is>
           <t>110.060226,110.099640,109.920517,109.975746,109.932312,109.961761,109.945755,109.667114,109.821564,109.920967,109.687134,109.762306,109.890709,109.874390,109.943481,109.758194,109.868591,109.997086,110.069763,109.794250,109.896423,109.710892,109.878044,109.976036</t>
@@ -8734,6 +8790,49 @@
       <c r="M84" t="inlineStr">
         <is>
           <t>109.390076,109.088303,108.953217,108.794685,108.711884,108.593010,108.450233,108.306541,108.315765,108.098862,107.877869,107.841431,107.761635,107.686264,107.802536,107.577530,107.606018,107.372658,107.365128,107.352608,107.220428,107.103745,107.161705,107.125961</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-10-11 05:28:17</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>24</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>109.593765,109.565048,109.542419,109.486603,109.594086,109.552521,109.550659,109.539925,109.485443,109.468582,109.485817,109.467110,109.448616,109.485550,109.514572,109.453415,109.519119,109.467514,109.466629,109.487038,109.375252,109.484352,109.439949,109.470825</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>109.549049,109.479172,109.411476,109.502075,109.508858,109.485825,109.549011,109.448715,109.512871,109.540131,109.487732,109.435471,109.525627,109.460991,109.545677,109.423309,109.600372,109.612930,109.544502,109.492538,109.634216,109.416260,109.475433,109.442932</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>108.700104,108.442665,108.290161,108.149513,108.115555,107.983170,107.886353,107.762283,107.625587,107.516205,107.447403,107.275230,107.112579,107.089691,107.065941,106.726471,106.761703,106.564865,106.339592,106.317207,106.096985,106.106987,106.044060,105.864609</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>109.087822,108.871696,108.768898,108.638710,108.671158,108.583481,108.482384,108.421066,108.462082,108.262680,108.219688,108.129868,108.052315,108.027245,108.144104,107.884941,107.937714,107.741844,107.729996,107.693916,107.522537,107.492668,107.454460,107.316681</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:J86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3647,6 +3647,44 @@
       </c>
       <c r="F85" t="n">
         <v>109.4708251953125</v>
+      </c>
+      <c r="G85" t="n">
+        <v>112.5999984741211</v>
+      </c>
+      <c r="H85" t="n">
+        <v>3.129173278808594</v>
+      </c>
+      <c r="I85" t="n">
+        <v>2.779017159158997</v>
+      </c>
+      <c r="J85" t="n">
+        <v>1.280018075338035</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-10-12 05:39:25</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>24</v>
+      </c>
+      <c r="F86" t="n">
+        <v>112.7169647216797</v>
       </c>
     </row>
   </sheetData>
@@ -3660,7 +3698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M85"/>
+  <dimension ref="A1:M86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8820,6 +8858,24 @@
           <t>109.593765,109.565048,109.542419,109.486603,109.594086,109.552521,109.550659,109.539925,109.485443,109.468582,109.485817,109.467110,109.448616,109.485550,109.514572,109.453415,109.519119,109.467514,109.466629,109.487038,109.375252,109.484352,109.439949,109.470825</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>109.720001,109.300003,109.400002,109.389999,109.230003,109.489998,109.410004,109.349998,109.650002,111.830002,112.199997,112.010002,111.430000,111.239998,111.220001,110.620003,110.949997,111.209999,111.500000,111.489998,111.910004,111.559998,113.029999,112.599998</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>0.126236,0.265045,0.142417,0.096604,0.364083,0.062523,0.140655,0.189927,0.164559,2.361420,2.714180,2.542892,1.981384,1.754448,1.705429,1.166588,1.430878,1.742485,2.033371,2.002960,2.534752,2.075646,3.590050,3.129173</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>0.115053,0.242493,0.130181,0.088311,0.333317,0.057104,0.128558,0.173687,0.150076,2.111616,2.419055,2.270237,1.778143,1.577174,1.533384,1.054590,1.289660,1.566842,1.823651,1.796538,2.264991,1.860564,3.176192,2.779017</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>1.280018075338035</v>
+      </c>
       <c r="K85" t="inlineStr">
         <is>
           <t>109.549049,109.479172,109.411476,109.502075,109.508858,109.485825,109.549011,109.448715,109.512871,109.540131,109.487732,109.435471,109.525627,109.460991,109.545677,109.423309,109.600372,109.612930,109.544502,109.492538,109.634216,109.416260,109.475433,109.442932</t>
@@ -8833,6 +8889,49 @@
       <c r="M85" t="inlineStr">
         <is>
           <t>109.087822,108.871696,108.768898,108.638710,108.671158,108.583481,108.482384,108.421066,108.462082,108.262680,108.219688,108.129868,108.052315,108.027245,108.144104,107.884941,107.937714,107.741844,107.729996,107.693916,107.522537,107.492668,107.454460,107.316681</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-10-12 05:39:25</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>24</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>112.457024,112.492554,112.527275,112.534607,112.637093,112.645187,112.698982,112.681068,112.672600,112.669647,112.765488,112.766571,112.775360,112.720154,112.760796,112.746002,112.764099,112.712662,112.707672,112.694382,112.605316,112.655159,112.667564,112.716965</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>112.566093,112.445549,112.471390,112.531219,112.537888,112.588104,112.609375,112.574509,112.694641,112.621300,112.713844,112.622818,112.739334,112.653305,112.744919,112.771606,112.779724,112.688293,112.708572,112.748138,112.686829,112.715439,112.623337,112.548965</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>111.409927,111.153038,110.916595,110.805237,110.710358,110.664177,110.545700,110.440819,110.281082,110.192581,110.156982,110.129089,110.060860,110.012566,109.941956,109.790924,109.732796,109.606277,109.330147,109.241798,109.161385,109.152847,109.097900,109.057968</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>111.863144,111.678314,111.524384,111.474602,111.406799,111.354782,111.298950,111.245941,111.252121,111.108566,111.103073,111.108871,111.120117,111.030670,111.065948,110.950150,110.970551,110.775414,110.684540,110.667114,110.507538,110.503891,110.493103,110.519012</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J86"/>
+  <dimension ref="A1:J87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3685,6 +3685,44 @@
       </c>
       <c r="F86" t="n">
         <v>112.7169647216797</v>
+      </c>
+      <c r="G86" t="n">
+        <v>108.3600006103516</v>
+      </c>
+      <c r="H86" t="n">
+        <v>4.356964111328139</v>
+      </c>
+      <c r="I86" t="n">
+        <v>4.020823262077318</v>
+      </c>
+      <c r="J86" t="n">
+        <v>3.846907644792671</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-10-13 06:35:41</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>24</v>
+      </c>
+      <c r="F87" t="n">
+        <v>109.4744415283203</v>
       </c>
     </row>
   </sheetData>
@@ -3698,7 +3736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M86"/>
+  <dimension ref="A1:M87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8919,6 +8957,24 @@
           <t>112.457024,112.492554,112.527275,112.534607,112.637093,112.645187,112.698982,112.681068,112.672600,112.669647,112.765488,112.766571,112.775360,112.720154,112.760796,112.746002,112.764099,112.712662,112.707672,112.694382,112.605316,112.655159,112.667564,112.716965</t>
         </is>
       </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>112.540001,112.480003,111.610001,111.629997,111.540001,110.910004,110.139999,110.379997,108.669998,108.779999,107.709999,107.650002,107.430000,108.190002,108.339996,107.089996,106.300003,105.629997,102.830002,105.230003,106.629997,107.349998,107.949997,108.360001</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>0.082977,0.012551,0.917274,0.904610,1.097092,1.735183,2.558983,2.301071,4.002602,3.889648,5.055489,5.116569,5.345360,4.530152,4.420800,5.656006,6.464096,7.082665,9.877670,7.464379,5.975319,5.305161,4.717567,4.356964</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>0.073731,0.011158,0.821857,0.810364,0.983586,1.564497,2.323391,2.084681,3.683263,3.575702,4.693612,4.752967,4.975668,4.187218,4.080487,5.281544,6.080993,6.705164,9.605825,7.093394,5.603788,4.941929,4.370141,4.020824</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>3.846907644792671</v>
+      </c>
       <c r="K86" t="inlineStr">
         <is>
           <t>112.566093,112.445549,112.471390,112.531219,112.537888,112.588104,112.609375,112.574509,112.694641,112.621300,112.713844,112.622818,112.739334,112.653305,112.744919,112.771606,112.779724,112.688293,112.708572,112.748138,112.686829,112.715439,112.623337,112.548965</t>
@@ -8932,6 +8988,49 @@
       <c r="M86" t="inlineStr">
         <is>
           <t>111.863144,111.678314,111.524384,111.474602,111.406799,111.354782,111.298950,111.245941,111.252121,111.108566,111.103073,111.108871,111.120117,111.030670,111.065948,110.950150,110.970551,110.775414,110.684540,110.667114,110.507538,110.503891,110.493103,110.519012</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-10-13 06:35:41</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>24</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>108.682823,108.773750,108.776093,108.846603,108.918594,108.984924,109.007675,109.033279,109.099304,109.145523,109.114838,109.253265,109.221252,109.247925,109.191483,109.271111,109.249329,109.278145,109.301941,109.330528,109.339066,109.342278,109.421921,109.474442</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>108.802383,109.040688,108.796432,108.942268,108.984436,108.997803,109.274689,109.051277,109.353424,109.167816,109.238770,109.316277,109.482986,109.519333,109.368774,109.312698,109.519943,109.653145,109.628922,109.576324,109.392578,109.368103,109.671486,109.628922</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>107.606674,107.347939,107.028305,106.769424,106.600510,106.484787,106.256065,105.996170,105.962433,105.697937,105.565750,105.490738,105.381683,105.251938,105.096268,104.987885,104.796021,104.684570,104.302834,104.246666,104.229424,104.203339,104.284081,104.221848</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>108.046577,107.894699,107.624458,107.550018,107.453934,107.348152,107.201584,107.038734,107.056747,106.885468,106.692047,106.837486,106.673218,106.602890,106.569283,106.485672,106.404587,106.196243,106.181953,106.165497,106.164658,106.162170,106.232414,106.232628</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J87"/>
+  <dimension ref="A1:J88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3723,6 +3723,44 @@
       </c>
       <c r="F87" t="n">
         <v>109.4744415283203</v>
+      </c>
+      <c r="G87" t="n">
+        <v>108.129997253418</v>
+      </c>
+      <c r="H87" t="n">
+        <v>1.34444427490233</v>
+      </c>
+      <c r="I87" t="n">
+        <v>1.243359205634153</v>
+      </c>
+      <c r="J87" t="n">
+        <v>1.725650996487774</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-10-14 04:36:19</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>24</v>
+      </c>
+      <c r="F88" t="n">
+        <v>108.4786911010742</v>
       </c>
     </row>
   </sheetData>
@@ -3736,7 +3774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M87"/>
+  <dimension ref="A1:M88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9018,6 +9056,24 @@
           <t>108.682823,108.773750,108.776093,108.846603,108.918594,108.984924,109.007675,109.033279,109.099304,109.145523,109.114838,109.253265,109.221252,109.247925,109.191483,109.271111,109.249329,109.278145,109.301941,109.330528,109.339066,109.342278,109.421921,109.474442</t>
         </is>
       </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>108.459999,107.529999,106.900002,106.389999,106.050003,106.559998,106.660004,107.419998,107.260002,107.449997,107.040001,107.739998,107.400002,107.019997,107.010002,106.919998,106.730003,107.330002,107.320000,107.629997,107.730003,108.129997,108.129997,108.129997</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>0.222824,1.243751,1.876091,2.456604,2.868591,2.424926,2.347671,1.613281,1.839302,1.695526,2.074837,1.513267,1.821250,2.227928,2.181481,2.351113,2.519326,1.948143,1.981941,1.700531,1.609063,1.212281,1.291924,1.344445</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>0.205443,1.156655,1.754997,2.309055,2.704942,2.275644,2.201079,1.501844,1.714807,1.577968,1.938375,1.404555,1.695764,2.081787,2.038577,2.198946,2.360466,1.815097,1.846759,1.579978,1.493607,1.121133,1.194788,1.243360</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>1.725650996487774</v>
+      </c>
       <c r="K87" t="inlineStr">
         <is>
           <t>108.802383,109.040688,108.796432,108.942268,108.984436,108.997803,109.274689,109.051277,109.353424,109.167816,109.238770,109.316277,109.482986,109.519333,109.368774,109.312698,109.519943,109.653145,109.628922,109.576324,109.392578,109.368103,109.671486,109.628922</t>
@@ -9031,6 +9087,49 @@
       <c r="M87" t="inlineStr">
         <is>
           <t>108.046577,107.894699,107.624458,107.550018,107.453934,107.348152,107.201584,107.038734,107.056747,106.885468,106.692047,106.837486,106.673218,106.602890,106.569283,106.485672,106.404587,106.196243,106.181953,106.165497,106.164658,106.162170,106.232414,106.232628</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-10-14 04:36:19</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>24</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>108.099648,108.153076,108.146393,108.159859,108.231590,108.245590,108.217163,108.202728,108.264481,108.253204,108.225410,108.297859,108.353424,108.368515,108.317932,108.388321,108.357391,108.387772,108.420395,108.438187,108.513939,108.461693,108.466362,108.478691</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>108.199730,108.214211,108.093475,108.252388,108.369957,108.175041,108.404518,108.278328,108.456017,108.243889,108.304337,108.415108,108.601578,108.583435,108.541412,108.471085,108.641205,108.734222,108.700142,108.641495,108.548416,108.504509,108.674736,108.649681</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>107.210083,107.011452,106.690010,106.530640,106.389893,106.312378,106.177231,105.978333,105.883102,105.673325,105.545700,105.502464,105.343987,105.224220,105.096069,104.990700,104.888351,104.835686,104.476105,104.475197,104.486893,104.415878,104.353844,104.250740</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>107.583679,107.413040,107.177361,107.103432,107.113388,106.993019,106.927704,106.802551,106.838959,106.670212,106.508545,106.602036,106.467102,106.335503,106.327370,106.244003,106.149063,106.029419,106.068382,106.075890,106.057892,105.997925,105.982231,105.954575</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J88"/>
+  <dimension ref="A1:J89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3761,6 +3761,44 @@
       </c>
       <c r="F88" t="n">
         <v>108.4786911010742</v>
+      </c>
+      <c r="G88" t="n">
+        <v>102.7200012207031</v>
+      </c>
+      <c r="H88" t="n">
+        <v>5.75868988037108</v>
+      </c>
+      <c r="I88" t="n">
+        <v>5.606201140903433</v>
+      </c>
+      <c r="J88" t="n">
+        <v>3.245692922021657</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-10-15 04:18:54</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>24</v>
+      </c>
+      <c r="F89" t="n">
+        <v>102.3773880004883</v>
       </c>
     </row>
   </sheetData>
@@ -3774,7 +3812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M88"/>
+  <dimension ref="A1:M89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9117,6 +9155,24 @@
           <t>108.099648,108.153076,108.146393,108.159859,108.231590,108.245590,108.217163,108.202728,108.264481,108.253204,108.225410,108.297859,108.353424,108.368515,108.317932,108.388321,108.357391,108.387772,108.420395,108.438187,108.513939,108.461693,108.466362,108.478691</t>
         </is>
       </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>107.080002,107.059998,107.370003,106.910004,106.500000,107.089996,107.070000,105.339996,104.820000,104.290001,103.750000,104.849998,104.279999,104.230003,104.080002,103.980003,104.610001,104.419998,104.160004,104.220001,103.870003,103.190002,102.370003,102.720001</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>1.019646,1.093078,0.776390,1.249855,1.731590,1.155594,1.147163,2.862732,3.444481,3.963203,4.475410,3.447861,4.073425,4.138512,4.237930,4.408318,3.747390,3.967774,4.260391,4.218186,4.643936,5.271691,6.096359,5.758690</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>0.952228,1.020996,0.723098,1.169072,1.625906,1.079086,1.071414,2.717611,3.286092,3.800176,4.313648,3.288374,3.906238,3.970557,4.071801,4.239582,3.582249,3.799822,4.090237,4.047386,4.470912,5.108722,5.955220,5.606201</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>3.245692922021657</v>
+      </c>
       <c r="K88" t="inlineStr">
         <is>
           <t>108.199730,108.214211,108.093475,108.252388,108.369957,108.175041,108.404518,108.278328,108.456017,108.243889,108.304337,108.415108,108.601578,108.583435,108.541412,108.471085,108.641205,108.734222,108.700142,108.641495,108.548416,108.504509,108.674736,108.649681</t>
@@ -9130,6 +9186,49 @@
       <c r="M88" t="inlineStr">
         <is>
           <t>107.583679,107.413040,107.177361,107.103432,107.113388,106.993019,106.927704,106.802551,106.838959,106.670212,106.508545,106.602036,106.467102,106.335503,106.327370,106.244003,106.149063,106.029419,106.068382,106.075890,106.057892,105.997925,105.982231,105.954575</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-10-15 04:18:54</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>24</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>102.662903,102.661743,102.544006,102.471535,102.507164,102.435532,102.354370,102.411919,102.437019,102.463684,102.362930,102.434746,102.414581,102.488312,102.466751,102.496696,102.497330,102.562607,102.559036,102.519165,102.545517,102.505371,102.381889,102.377388</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>102.727623,102.666824,102.543060,102.690567,102.689926,102.469017,102.553131,102.460670,102.659424,102.708138,102.496475,102.751495,102.866516,102.793793,102.776871,102.732300,102.906479,103.047798,102.916893,102.946472,102.768105,102.593269,102.854195,102.789108</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>101.662384,101.463348,101.091354,100.858963,100.764709,100.604179,100.542259,100.427979,100.362213,100.230957,100.033791,99.967422,99.829315,99.766785,99.703262,99.579720,99.488655,99.495903,99.233238,99.070412,99.005295,98.979584,98.809662,98.651344</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>102.002808,101.904633,101.629921,101.440247,101.440178,101.334167,101.216293,101.169106,101.218269,101.048088,100.818932,100.976692,100.792038,100.729584,100.811333,100.694717,100.632599,100.570633,100.610229,100.455322,100.395897,100.388672,100.184128,100.200684</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J89"/>
+  <dimension ref="A1:J90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3799,6 +3799,44 @@
       </c>
       <c r="F89" t="n">
         <v>102.3773880004883</v>
+      </c>
+      <c r="G89" t="n">
+        <v>105.1699981689453</v>
+      </c>
+      <c r="H89" t="n">
+        <v>2.792610168457017</v>
+      </c>
+      <c r="I89" t="n">
+        <v>2.655329672984269</v>
+      </c>
+      <c r="J89" t="n">
+        <v>2.035889594235667</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:14:28</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>24</v>
+      </c>
+      <c r="F90" t="n">
+        <v>104.7006530761719</v>
       </c>
     </row>
   </sheetData>
@@ -3812,7 +3850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M89"/>
+  <dimension ref="A1:M90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9216,6 +9254,24 @@
           <t>102.662903,102.661743,102.544006,102.471535,102.507164,102.435532,102.354370,102.411919,102.437019,102.463684,102.362930,102.434746,102.414581,102.488312,102.466751,102.496696,102.497330,102.562607,102.559036,102.519165,102.545517,102.505371,102.381889,102.377388</t>
         </is>
       </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>101.339996,102.010002,103.150002,103.190002,103.040001,102.260002,102.070000,101.570000,101.430000,104.730003,105.989998,105.489998,105.809998,105.849998,105.940002,105.550003,105.919998,105.720001,105.269997,105.440002,105.000000,105.209999,105.199997,105.169998</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>1.322907,0.651741,0.605996,0.718467,0.532837,0.175530,0.284370,0.841919,1.007019,2.266319,3.627068,3.055252,3.395417,3.361686,3.473251,3.053307,3.422668,3.157394,2.710961,2.920837,2.454483,2.704628,2.818108,2.792610</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1.305414,0.638899,0.587490,0.696257,0.517117,0.171651,0.278603,0.828905,0.992821,2.163964,3.422085,2.896248,3.208975,3.175897,3.278508,2.892759,3.231371,2.986563,2.575245,2.770142,2.337603,2.570695,2.678810,2.655330</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>2.035889594235667</v>
+      </c>
       <c r="K89" t="inlineStr">
         <is>
           <t>102.727623,102.666824,102.543060,102.690567,102.689926,102.469017,102.553131,102.460670,102.659424,102.708138,102.496475,102.751495,102.866516,102.793793,102.776871,102.732300,102.906479,103.047798,102.916893,102.946472,102.768105,102.593269,102.854195,102.789108</t>
@@ -9229,6 +9285,49 @@
       <c r="M89" t="inlineStr">
         <is>
           <t>102.002808,101.904633,101.629921,101.440247,101.440178,101.334167,101.216293,101.169106,101.218269,101.048088,100.818932,100.976692,100.792038,100.729584,100.811333,100.694717,100.632599,100.570633,100.610229,100.455322,100.395897,100.388672,100.184128,100.200684</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:14:28</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>24</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>105.074196,105.082115,105.014687,104.979919,105.013329,105.035355,104.983063,104.998283,105.052223,105.036446,105.037277,104.959167,104.937454,104.999611,104.949409,104.921829,104.953491,104.928818,104.863113,104.790184,104.787827,104.729683,104.680954,104.700653</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>105.183304,104.928925,105.057953,105.109520,105.008080,105.099106,105.037300,105.090927,105.251694,105.156494,105.197197,105.216309,105.184464,105.207550,105.279129,105.111176,105.303329,105.104416,105.006340,105.202148,104.985558,105.008942,104.926193,104.977928</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>103.917389,103.633537,103.262230,103.023384,102.995659,102.883667,102.672867,102.512115,102.522980,102.417900,102.278610,102.075653,101.942146,101.935295,101.803162,101.562912,101.449104,101.414871,101.096924,100.909805,100.883171,100.751740,100.678513,100.588829</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>104.325821,104.206955,103.896774,103.817284,103.751747,103.667725,103.589935,103.492195,103.519882,103.357285,103.204163,103.208542,103.028946,102.984932,103.055336,102.886124,102.779976,102.613380,102.578766,102.390297,102.337753,102.286682,102.170082,102.185852</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/SOL-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J90"/>
+  <dimension ref="A1:J91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3837,6 +3837,44 @@
       </c>
       <c r="F90" t="n">
         <v>104.7006530761719</v>
+      </c>
+      <c r="G90" t="n">
+        <v>104.7300033569336</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0.02935028076169033</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0.02802471099104305</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0.9056177891862303</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-10-17 04:04:35</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>24</v>
+      </c>
+      <c r="F91" t="n">
+        <v>104.146369934082</v>
       </c>
     </row>
   </sheetData>
@@ -3850,7 +3888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M90"/>
+  <dimension ref="A1:M91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9315,6 +9353,24 @@
           <t>105.074196,105.082115,105.014687,104.979919,105.013329,105.035355,104.983063,104.998283,105.052223,105.036446,105.037277,104.959167,104.937454,104.999611,104.949409,104.921829,104.953491,104.928818,104.863113,104.790184,104.787827,104.729683,104.680954,104.700653</t>
         </is>
       </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>105.830002,106.209999,106.230003,106.699997,106.169998,106.639999,106.470001,105.519997,105.589996,105.529999,103.650002,103.900002,103.559998,102.940002,103.400002,103.919998,104.059998,104.269997,104.320000,104.230003,104.169998,104.440002,104.830002,104.730003</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>0.755806,1.127884,1.215316,1.720078,1.156669,1.604644,1.486938,0.521714,0.537773,0.493553,1.387275,1.059165,1.377456,2.059609,1.549407,1.001831,0.893493,0.658821,0.543113,0.560181,0.617829,0.289681,0.149048,0.029350</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>0.714170,1.061938,1.144042,1.612069,1.089450,1.504730,1.396580,0.494422,0.509303,0.467690,1.338423,1.019409,1.330105,2.000785,1.498460,0.964040,0.858633,0.631842,0.520622,0.537447,0.593097,0.277366,0.142181,0.028025</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>0.9056177891862303</v>
+      </c>
       <c r="K90" t="inlineStr">
         <is>
           <t>105.183304,104.928925,105.057953,105.109520,105.008080,105.099106,105.037300,105.090927,105.251694,105.156494,105.197197,105.216309,105.184464,105.207550,105.279129,105.111176,105.303329,105.104416,105.006340,105.202148,104.985558,105.008942,104.926193,104.977928</t>
@@ -9328,6 +9384,49 @@
       <c r="M90" t="inlineStr">
         <is>
           <t>104.325821,104.206955,103.896774,103.817284,103.751747,103.667725,103.589935,103.492195,103.519882,103.357285,103.204163,103.208542,103.028946,102.984932,103.055336,102.886124,102.779976,102.613380,102.578766,102.390297,102.337753,102.286682,102.170082,102.185852</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-10-17 04:04:35</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>SOL-USD</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>24</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>104.652618,104.671585,104.635437,104.609909,104.643997,104.619308,104.545334,104.514595,104.495163,104.481201,104.416794,104.310440,104.321396,104.362404,104.269768,104.258453,104.211937,104.284012,104.260803,104.161041,104.177048,104.145142,104.162727,104.146370</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>104.775894,104.744034,104.693283,104.702057,104.712357,104.695969,104.726089,104.503082,104.743256,104.557869,104.470840,104.696648,104.749420,104.467133,104.488350,104.456367,104.468658,104.617538,104.488846,104.558350,104.494331,104.461609,104.314873,104.541061</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>103.691666,103.554657,103.324066,103.199646,103.175247,103.123619,102.934357,102.752235,102.701111,102.586304,102.422676,102.138458,102.055222,101.966019,101.877167,101.759171,101.528343,101.597229,101.343552,101.128174,101.101288,101.068153,101.016251,100.885162</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>103.988693,104.020920,103.847641,103.784424,103.720291,103.727081,103.596909,103.485817,103.487915,103.307190,103.097183,103.033508,102.913834,102.870888,102.865929,102.815147,102.561562,102.606071,102.569107,102.356613,102.288696,102.302101,102.234894,102.131424</t>
         </is>
       </c>
     </row>
